--- a/output/full_scan/batch_seq0_2026-07-16.xlsx
+++ b/output/full_scan/batch_seq0_2026-07-16.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O115"/>
+  <dimension ref="A1:O117"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -1534,21 +1534,21 @@
     </row>
     <row r="21">
       <c r="A21" s="2" t="n">
-        <v>8926</v>
+        <v>8096</v>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>台汽電</t>
+          <t>擎亞</t>
         </is>
       </c>
       <c r="C21" s="2" t="n">
         <v/>
       </c>
       <c r="D21" s="2" t="n">
-        <v>470.5502459669697</v>
+        <v>471.5431715912845</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>67</v>
+        <v>142</v>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
@@ -1559,13 +1559,13 @@
         <v>0</v>
       </c>
       <c r="H21" s="2" t="n">
-        <v>40.13676784216944</v>
+        <v>46.7046566285066</v>
       </c>
       <c r="I21" s="2" t="n">
-        <v>32.12251835766028</v>
+        <v>27.51668491094916</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>0.3666812635556858</v>
+        <v>0.248433308162794</v>
       </c>
       <c r="K21" s="2" t="n">
         <v>0</v>
@@ -1577,7 +1577,7 @@
         <v>-1</v>
       </c>
       <c r="N21" s="2" t="n">
-        <v>-1.888846585239672</v>
+        <v>-2.840307164093828</v>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
@@ -1587,21 +1587,21 @@
     </row>
     <row r="22">
       <c r="A22" s="2" t="n">
-        <v>8183</v>
+        <v>8926</v>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>精星</t>
+          <t>台汽電</t>
         </is>
       </c>
       <c r="C22" s="2" t="n">
         <v/>
       </c>
       <c r="D22" s="2" t="n">
-        <v>469.155603189103</v>
+        <v>470.5502459669697</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>32.05</v>
+        <v>67</v>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
@@ -1612,13 +1612,13 @@
         <v>0</v>
       </c>
       <c r="H22" s="2" t="n">
-        <v>44.17490543030802</v>
+        <v>40.13676784216944</v>
       </c>
       <c r="I22" s="2" t="n">
-        <v>23.7157611277203</v>
+        <v>32.12251835766028</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>0.8021521783185755</v>
+        <v>0.3666812635556858</v>
       </c>
       <c r="K22" s="2" t="n">
         <v>0</v>
@@ -1630,31 +1630,31 @@
         <v>-1</v>
       </c>
       <c r="N22" s="2" t="n">
-        <v>-0.1615170335201879</v>
+        <v>-1.888846585239672</v>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="n">
-        <v>8121</v>
+        <v>8183</v>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>越峰</t>
+          <t>精星</t>
         </is>
       </c>
       <c r="C23" s="2" t="n">
         <v/>
       </c>
       <c r="D23" s="2" t="n">
-        <v>457.4210950428837</v>
+        <v>469.155603189103</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>39.45</v>
+        <v>32.05</v>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
@@ -1665,13 +1665,13 @@
         <v>0</v>
       </c>
       <c r="H23" s="2" t="n">
-        <v>39.43404021164215</v>
+        <v>44.17490543030802</v>
       </c>
       <c r="I23" s="2" t="n">
-        <v>24.27813965047455</v>
+        <v>23.7157611277203</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>0.3233095157458435</v>
+        <v>0.8021521783185755</v>
       </c>
       <c r="K23" s="2" t="n">
         <v>0</v>
@@ -1683,31 +1683,31 @@
         <v>-1</v>
       </c>
       <c r="N23" s="2" t="n">
-        <v>-1.438785994009133</v>
+        <v>-0.1615170335201879</v>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="n">
-        <v>8093</v>
+        <v>8121</v>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>保銳</t>
+          <t>越峰</t>
         </is>
       </c>
       <c r="C24" s="2" t="n">
         <v/>
       </c>
       <c r="D24" s="2" t="n">
-        <v>452.0011231118459</v>
+        <v>457.4210950428837</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>19.5</v>
+        <v>39.45</v>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
@@ -1718,13 +1718,13 @@
         <v>0</v>
       </c>
       <c r="H24" s="2" t="n">
-        <v>50.79839137393841</v>
+        <v>39.43404021164215</v>
       </c>
       <c r="I24" s="2" t="n">
-        <v>10.2028328230347</v>
+        <v>24.27813965047455</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>1.358234184395772</v>
+        <v>0.3233095157458435</v>
       </c>
       <c r="K24" s="2" t="n">
         <v>0</v>
@@ -1736,31 +1736,31 @@
         <v>-1</v>
       </c>
       <c r="N24" s="2" t="n">
-        <v>-0.06252660983520369</v>
+        <v>-1.438785994009133</v>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="n">
-        <v>9905</v>
+        <v>8093</v>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>大華</t>
+          <t>保銳</t>
         </is>
       </c>
       <c r="C25" s="2" t="n">
         <v/>
       </c>
       <c r="D25" s="2" t="n">
-        <v>441.6725900578032</v>
+        <v>452.0011231118459</v>
       </c>
       <c r="E25" s="2" t="n">
-        <v>20.75</v>
+        <v>19.5</v>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
@@ -1771,13 +1771,13 @@
         <v>0</v>
       </c>
       <c r="H25" s="2" t="n">
-        <v>44.94895992493829</v>
+        <v>50.79839137393841</v>
       </c>
       <c r="I25" s="2" t="n">
-        <v>24.90995169390703</v>
+        <v>10.2028328230347</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>0.3101441475823751</v>
+        <v>1.358234184395772</v>
       </c>
       <c r="K25" s="2" t="n">
         <v>0</v>
@@ -1789,31 +1789,31 @@
         <v>-1</v>
       </c>
       <c r="N25" s="2" t="n">
-        <v>-0.0686646397061316</v>
+        <v>-0.06252660983520369</v>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="n">
-        <v>8271</v>
+        <v>9905</v>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>宇瞻</t>
+          <t>大華</t>
         </is>
       </c>
       <c r="C26" s="2" t="n">
         <v/>
       </c>
       <c r="D26" s="2" t="n">
-        <v>436.044603705417</v>
+        <v>441.6725900578032</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>187.5</v>
+        <v>20.75</v>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
@@ -1824,13 +1824,13 @@
         <v>0</v>
       </c>
       <c r="H26" s="2" t="n">
-        <v>44.27320374782399</v>
+        <v>44.94895992493829</v>
       </c>
       <c r="I26" s="2" t="n">
-        <v>26.07159009428432</v>
+        <v>24.90995169390703</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>0.9662045998298248</v>
+        <v>0.3101441475823751</v>
       </c>
       <c r="K26" s="2" t="n">
         <v>0</v>
@@ -1842,31 +1842,31 @@
         <v>-1</v>
       </c>
       <c r="N26" s="2" t="n">
-        <v>-0.1438046226645219</v>
+        <v>-0.0686646397061316</v>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="n">
-        <v>8367</v>
+        <v>8271</v>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>建新國際</t>
+          <t>宇瞻</t>
         </is>
       </c>
       <c r="C27" s="2" t="n">
         <v/>
       </c>
       <c r="D27" s="2" t="n">
-        <v>421.8129129292285</v>
+        <v>436.044603705417</v>
       </c>
       <c r="E27" s="2" t="n">
-        <v>40.5</v>
+        <v>187.5</v>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
@@ -1877,13 +1877,13 @@
         <v>0</v>
       </c>
       <c r="H27" s="2" t="n">
-        <v>49.71728832167998</v>
+        <v>44.27320374782399</v>
       </c>
       <c r="I27" s="2" t="n">
-        <v>26.37792350471074</v>
+        <v>26.07159009428432</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>0.6241167888561371</v>
+        <v>0.9662045998298248</v>
       </c>
       <c r="K27" s="2" t="n">
         <v>0</v>
@@ -1895,31 +1895,31 @@
         <v>-1</v>
       </c>
       <c r="N27" s="2" t="n">
-        <v>0.0892222125419066</v>
+        <v>-0.1438046226645219</v>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="n">
-        <v>9136</v>
+        <v>8367</v>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>巨騰-DR</t>
+          <t>建新國際</t>
         </is>
       </c>
       <c r="C28" s="2" t="n">
         <v/>
       </c>
       <c r="D28" s="2" t="n">
-        <v>421.6207085895738</v>
+        <v>421.8129129292285</v>
       </c>
       <c r="E28" s="2" t="n">
-        <v>12.45</v>
+        <v>40.5</v>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
@@ -1930,13 +1930,13 @@
         <v>0</v>
       </c>
       <c r="H28" s="2" t="n">
-        <v>42.47894758438659</v>
+        <v>49.71728832167998</v>
       </c>
       <c r="I28" s="2" t="n">
-        <v>23.085264489106</v>
+        <v>26.37792350471074</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>0.8579427416186926</v>
+        <v>0.6241167888561371</v>
       </c>
       <c r="K28" s="2" t="n">
         <v>0</v>
@@ -1948,31 +1948,31 @@
         <v>-1</v>
       </c>
       <c r="N28" s="2" t="n">
-        <v>-0.4414938033298136</v>
+        <v>0.0892222125419066</v>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="n">
-        <v>8488</v>
+        <v>9136</v>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>吉源-KY</t>
+          <t>巨騰-DR</t>
         </is>
       </c>
       <c r="C29" s="2" t="n">
         <v/>
       </c>
       <c r="D29" s="2" t="n">
-        <v>413.4268993737946</v>
+        <v>421.6207085895738</v>
       </c>
       <c r="E29" s="2" t="n">
-        <v>10.25</v>
+        <v>12.45</v>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
@@ -1983,13 +1983,13 @@
         <v>0</v>
       </c>
       <c r="H29" s="2" t="n">
-        <v>52.14563643316</v>
+        <v>42.47894758438659</v>
       </c>
       <c r="I29" s="2" t="n">
-        <v>12.22736455711239</v>
+        <v>23.085264489106</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>0.1845175902925295</v>
+        <v>0.8579427416186926</v>
       </c>
       <c r="K29" s="2" t="n">
         <v>0</v>
@@ -2001,31 +2001,31 @@
         <v>-1</v>
       </c>
       <c r="N29" s="2" t="n">
-        <v>0.1084029571820138</v>
+        <v>-0.4414938033298136</v>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="n">
-        <v>8147</v>
+        <v>8488</v>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>正淩</t>
+          <t>吉源-KY</t>
         </is>
       </c>
       <c r="C30" s="2" t="n">
         <v/>
       </c>
       <c r="D30" s="2" t="n">
-        <v>410.6779308411301</v>
+        <v>413.4268993737946</v>
       </c>
       <c r="E30" s="2" t="n">
-        <v>140.5</v>
+        <v>10.25</v>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
@@ -2036,13 +2036,13 @@
         <v>0</v>
       </c>
       <c r="H30" s="2" t="n">
-        <v>40.42925807333427</v>
+        <v>52.14563643316</v>
       </c>
       <c r="I30" s="2" t="n">
-        <v>17.29461358700242</v>
+        <v>12.22736455711239</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>0.4447425454713662</v>
+        <v>0.1845175902925295</v>
       </c>
       <c r="K30" s="2" t="n">
         <v>0</v>
@@ -2054,31 +2054,31 @@
         <v>-1</v>
       </c>
       <c r="N30" s="2" t="n">
-        <v>-0.268775447115714</v>
+        <v>0.1084029571820138</v>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="n">
-        <v>8482</v>
+        <v>8147</v>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>商億-KY</t>
+          <t>正淩</t>
         </is>
       </c>
       <c r="C31" s="2" t="n">
         <v/>
       </c>
       <c r="D31" s="2" t="n">
-        <v>403.1444715194386</v>
+        <v>410.6779308411301</v>
       </c>
       <c r="E31" s="2" t="n">
-        <v>48.5</v>
+        <v>140.5</v>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
@@ -2089,13 +2089,13 @@
         <v>0</v>
       </c>
       <c r="H31" s="2" t="n">
-        <v>51.63865075222221</v>
+        <v>40.42925807333427</v>
       </c>
       <c r="I31" s="2" t="n">
-        <v>5.371882775123725</v>
+        <v>17.29461358700242</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>2.571547964726934</v>
+        <v>0.4447425454713662</v>
       </c>
       <c r="K31" s="2" t="n">
         <v>0</v>
@@ -2107,31 +2107,31 @@
         <v>-1</v>
       </c>
       <c r="N31" s="2" t="n">
-        <v>0.8995628610840199</v>
+        <v>-0.268775447115714</v>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="n">
-        <v>9908</v>
+        <v>8482</v>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>大台北</t>
+          <t>商億-KY</t>
         </is>
       </c>
       <c r="C32" s="2" t="n">
         <v/>
       </c>
       <c r="D32" s="2" t="n">
-        <v>396.1761563083343</v>
+        <v>403.1444715194386</v>
       </c>
       <c r="E32" s="2" t="n">
-        <v>29.15</v>
+        <v>48.5</v>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
@@ -2142,13 +2142,13 @@
         <v>0</v>
       </c>
       <c r="H32" s="2" t="n">
-        <v>37.31691155534591</v>
+        <v>51.63865075222221</v>
       </c>
       <c r="I32" s="2" t="n">
-        <v>24.52103322308174</v>
+        <v>5.371882775123725</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>0.5628932120465022</v>
+        <v>2.571547964726934</v>
       </c>
       <c r="K32" s="2" t="n">
         <v>0</v>
@@ -2160,31 +2160,31 @@
         <v>-1</v>
       </c>
       <c r="N32" s="2" t="n">
-        <v>-0.07037235092267741</v>
+        <v>0.8995628610840199</v>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>volume_break, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="n">
-        <v>8442</v>
+        <v>9908</v>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>威宏-KY</t>
+          <t>大台北</t>
         </is>
       </c>
       <c r="C33" s="2" t="n">
         <v/>
       </c>
       <c r="D33" s="2" t="n">
-        <v>394.8576723047144</v>
+        <v>396.1761563083343</v>
       </c>
       <c r="E33" s="2" t="n">
-        <v>45.6</v>
+        <v>29.15</v>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
@@ -2195,13 +2195,13 @@
         <v>0</v>
       </c>
       <c r="H33" s="2" t="n">
-        <v>61.05455032628477</v>
+        <v>37.31691155534591</v>
       </c>
       <c r="I33" s="2" t="n">
-        <v>39.09974623504935</v>
+        <v>24.52103322308174</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>0.442262288716738</v>
+        <v>0.5628932120465022</v>
       </c>
       <c r="K33" s="2" t="n">
         <v>0</v>
@@ -2213,31 +2213,31 @@
         <v>-1</v>
       </c>
       <c r="N33" s="2" t="n">
-        <v>0.5551611996721648</v>
+        <v>-0.07037235092267741</v>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, adx_trending, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="n">
-        <v>8438</v>
+        <v>8442</v>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>昶昕</t>
+          <t>威宏-KY</t>
         </is>
       </c>
       <c r="C34" s="2" t="n">
         <v/>
       </c>
       <c r="D34" s="2" t="n">
-        <v>387.6627503190381</v>
+        <v>394.8576723047144</v>
       </c>
       <c r="E34" s="2" t="n">
-        <v>85.09999999999999</v>
+        <v>45.6</v>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
@@ -2248,13 +2248,13 @@
         <v>0</v>
       </c>
       <c r="H34" s="2" t="n">
-        <v>40.41948435800155</v>
+        <v>61.05455032628477</v>
       </c>
       <c r="I34" s="2" t="n">
-        <v>25.61920147952792</v>
+        <v>39.09974623504935</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>0.2615748275756921</v>
+        <v>0.442262288716738</v>
       </c>
       <c r="K34" s="2" t="n">
         <v>0</v>
@@ -2266,31 +2266,31 @@
         <v>-1</v>
       </c>
       <c r="N34" s="2" t="n">
-        <v>-1.597148931455401</v>
+        <v>0.5551611996721648</v>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
+          <t>rsi_strong, market_above_ma60, avoid_chase, adx_trending, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="n">
-        <v>9907</v>
+        <v>8438</v>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>統一實</t>
+          <t>昶昕</t>
         </is>
       </c>
       <c r="C35" s="2" t="n">
         <v/>
       </c>
       <c r="D35" s="2" t="n">
-        <v>387.5985500018053</v>
+        <v>387.6627503190381</v>
       </c>
       <c r="E35" s="2" t="n">
-        <v>15.3</v>
+        <v>85.09999999999999</v>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
@@ -2301,13 +2301,13 @@
         <v>0</v>
       </c>
       <c r="H35" s="2" t="n">
-        <v>42.31888044056613</v>
+        <v>40.41948435800155</v>
       </c>
       <c r="I35" s="2" t="n">
-        <v>24.9808106125969</v>
+        <v>25.61920147952792</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>0.6783315346011365</v>
+        <v>0.2615748275756921</v>
       </c>
       <c r="K35" s="2" t="n">
         <v>0</v>
@@ -2319,31 +2319,31 @@
         <v>-1</v>
       </c>
       <c r="N35" s="2" t="n">
-        <v>0.0365461532789588</v>
+        <v>-1.597148931455401</v>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="n">
-        <v>8081</v>
+        <v>9907</v>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>致新</t>
+          <t>統一實</t>
         </is>
       </c>
       <c r="C36" s="2" t="n">
         <v/>
       </c>
       <c r="D36" s="2" t="n">
-        <v>375.6779288362791</v>
+        <v>387.5985500018053</v>
       </c>
       <c r="E36" s="2" t="n">
-        <v>254</v>
+        <v>15.3</v>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
@@ -2354,13 +2354,13 @@
         <v>0</v>
       </c>
       <c r="H36" s="2" t="n">
-        <v>34.3304791093345</v>
+        <v>42.31888044056613</v>
       </c>
       <c r="I36" s="2" t="n">
-        <v>26.34663083578389</v>
+        <v>24.9808106125969</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>0.9731708529322436</v>
+        <v>0.6783315346011365</v>
       </c>
       <c r="K36" s="2" t="n">
         <v>0</v>
@@ -2372,31 +2372,31 @@
         <v>-1</v>
       </c>
       <c r="N36" s="2" t="n">
-        <v>-8.225440823723329</v>
+        <v>0.0365461532789588</v>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="n">
-        <v>8289</v>
+        <v>8081</v>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>泰藝</t>
+          <t>致新</t>
         </is>
       </c>
       <c r="C37" s="2" t="n">
         <v/>
       </c>
       <c r="D37" s="2" t="n">
-        <v>370.0811896333387</v>
+        <v>375.6779288362791</v>
       </c>
       <c r="E37" s="2" t="n">
-        <v>52.4</v>
+        <v>254</v>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
@@ -2407,13 +2407,13 @@
         <v>0</v>
       </c>
       <c r="H37" s="2" t="n">
-        <v>34.68494889675736</v>
+        <v>34.3304791093345</v>
       </c>
       <c r="I37" s="2" t="n">
-        <v>19.85370578552675</v>
+        <v>26.34663083578389</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>0.7332633009447093</v>
+        <v>0.9731708529322436</v>
       </c>
       <c r="K37" s="2" t="n">
         <v>0</v>
@@ -2425,31 +2425,31 @@
         <v>-1</v>
       </c>
       <c r="N37" s="2" t="n">
-        <v>-1.21910046410484</v>
+        <v>-8.225440823723329</v>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="n">
-        <v>8222</v>
+        <v>8289</v>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>寶一</t>
+          <t>泰藝</t>
         </is>
       </c>
       <c r="C38" s="2" t="n">
         <v/>
       </c>
       <c r="D38" s="2" t="n">
-        <v>369.0056975223414</v>
+        <v>370.0811896333387</v>
       </c>
       <c r="E38" s="2" t="n">
-        <v>40.2</v>
+        <v>52.4</v>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
@@ -2460,13 +2460,13 @@
         <v>0</v>
       </c>
       <c r="H38" s="2" t="n">
-        <v>54.1777229560573</v>
+        <v>34.68494889675736</v>
       </c>
       <c r="I38" s="2" t="n">
-        <v>29.57184126219017</v>
+        <v>19.85370578552675</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>0.2875537722468635</v>
+        <v>0.7332633009447093</v>
       </c>
       <c r="K38" s="2" t="n">
         <v>0</v>
@@ -2478,31 +2478,31 @@
         <v>-1</v>
       </c>
       <c r="N38" s="2" t="n">
-        <v>0.0797109353327973</v>
+        <v>-1.21910046410484</v>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="n">
-        <v>8068</v>
+        <v>8222</v>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>全達</t>
+          <t>寶一</t>
         </is>
       </c>
       <c r="C39" s="2" t="n">
         <v/>
       </c>
       <c r="D39" s="2" t="n">
-        <v>364.9308186017058</v>
+        <v>369.0056975223414</v>
       </c>
       <c r="E39" s="2" t="n">
-        <v>19.35</v>
+        <v>40.2</v>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
@@ -2513,13 +2513,13 @@
         <v>0</v>
       </c>
       <c r="H39" s="2" t="n">
-        <v>51.29338952307874</v>
+        <v>54.1777229560573</v>
       </c>
       <c r="I39" s="2" t="n">
-        <v>15.97671303395082</v>
+        <v>29.57184126219017</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>1.507976409441093</v>
+        <v>0.2875537722468635</v>
       </c>
       <c r="K39" s="2" t="n">
         <v>0</v>
@@ -2531,31 +2531,31 @@
         <v>-1</v>
       </c>
       <c r="N39" s="2" t="n">
-        <v>0.1397882420935043</v>
+        <v>0.0797109353327973</v>
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="n">
-        <v>8227</v>
+        <v>8068</v>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>巨有科技</t>
+          <t>全達</t>
         </is>
       </c>
       <c r="C40" s="2" t="n">
         <v/>
       </c>
       <c r="D40" s="2" t="n">
-        <v>364.4600203824459</v>
+        <v>364.9308186017058</v>
       </c>
       <c r="E40" s="2" t="n">
-        <v>163</v>
+        <v>19.35</v>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
@@ -2566,13 +2566,13 @@
         <v>0</v>
       </c>
       <c r="H40" s="2" t="n">
-        <v>37.73176496281615</v>
+        <v>51.29338952307874</v>
       </c>
       <c r="I40" s="2" t="n">
-        <v>16.11437120187196</v>
+        <v>15.97671303395082</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>0.2778113117403089</v>
+        <v>1.507976409441093</v>
       </c>
       <c r="K40" s="2" t="n">
         <v>0</v>
@@ -2584,31 +2584,31 @@
         <v>-1</v>
       </c>
       <c r="N40" s="2" t="n">
-        <v>-4.144476886500751</v>
+        <v>0.1397882420935043</v>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
+          <t>volume_break, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="n">
-        <v>8103</v>
+        <v>8227</v>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>瀚荃</t>
+          <t>巨有科技</t>
         </is>
       </c>
       <c r="C41" s="2" t="n">
         <v/>
       </c>
       <c r="D41" s="2" t="n">
-        <v>362.3780303274451</v>
+        <v>364.4600203824459</v>
       </c>
       <c r="E41" s="2" t="n">
-        <v>83.40000000000001</v>
+        <v>163</v>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
@@ -2619,13 +2619,13 @@
         <v>0</v>
       </c>
       <c r="H41" s="2" t="n">
-        <v>33.52977421256304</v>
+        <v>37.73176496281615</v>
       </c>
       <c r="I41" s="2" t="n">
-        <v>21.15976484780273</v>
+        <v>16.11437120187196</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>0.5054208194471063</v>
+        <v>0.2778113117403089</v>
       </c>
       <c r="K41" s="2" t="n">
         <v>0</v>
@@ -2637,31 +2637,31 @@
         <v>-1</v>
       </c>
       <c r="N41" s="2" t="n">
-        <v>-1.565220203421243</v>
+        <v>-4.144476886500751</v>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="n">
-        <v>8105</v>
+        <v>8103</v>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>凌巨</t>
+          <t>瀚荃</t>
         </is>
       </c>
       <c r="C42" s="2" t="n">
         <v/>
       </c>
       <c r="D42" s="2" t="n">
-        <v>361.5458546486183</v>
+        <v>362.3780303274451</v>
       </c>
       <c r="E42" s="2" t="n">
-        <v>17.65</v>
+        <v>83.40000000000001</v>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
@@ -2672,13 +2672,13 @@
         <v>0</v>
       </c>
       <c r="H42" s="2" t="n">
-        <v>36.58493636537622</v>
+        <v>33.52977421256304</v>
       </c>
       <c r="I42" s="2" t="n">
-        <v>28.2658210174348</v>
+        <v>21.15976484780273</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>0.2657777662214828</v>
+        <v>0.5054208194471063</v>
       </c>
       <c r="K42" s="2" t="n">
         <v>0</v>
@@ -2690,7 +2690,7 @@
         <v>-1</v>
       </c>
       <c r="N42" s="2" t="n">
-        <v>-0.7112933117654172</v>
+        <v>-1.565220203421243</v>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
@@ -2700,21 +2700,21 @@
     </row>
     <row r="43">
       <c r="A43" s="2" t="n">
-        <v>8234</v>
+        <v>8105</v>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>新漢</t>
+          <t>凌巨</t>
         </is>
       </c>
       <c r="C43" s="2" t="n">
         <v/>
       </c>
       <c r="D43" s="2" t="n">
-        <v>360.3649102284525</v>
+        <v>361.5458546486183</v>
       </c>
       <c r="E43" s="2" t="n">
-        <v>67.2</v>
+        <v>17.65</v>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
@@ -2725,13 +2725,13 @@
         <v>0</v>
       </c>
       <c r="H43" s="2" t="n">
-        <v>47.17539356444192</v>
+        <v>36.58493636537622</v>
       </c>
       <c r="I43" s="2" t="n">
-        <v>22.45536676768313</v>
+        <v>28.2658210174348</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>0.3229788322979507</v>
+        <v>0.2657777662214828</v>
       </c>
       <c r="K43" s="2" t="n">
         <v>0</v>
@@ -2743,31 +2743,31 @@
         <v>-1</v>
       </c>
       <c r="N43" s="2" t="n">
-        <v>-0.1485687960909136</v>
+        <v>-0.7112933117654172</v>
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="n">
-        <v>8088</v>
+        <v>8234</v>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>品安</t>
+          <t>新漢</t>
         </is>
       </c>
       <c r="C44" s="2" t="n">
         <v/>
       </c>
       <c r="D44" s="2" t="n">
-        <v>360.2063557022962</v>
+        <v>360.3649102284525</v>
       </c>
       <c r="E44" s="2" t="n">
-        <v>50.3</v>
+        <v>67.2</v>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
@@ -2778,16 +2778,16 @@
         <v>0</v>
       </c>
       <c r="H44" s="2" t="n">
-        <v>32.41050364806375</v>
+        <v>47.17539356444192</v>
       </c>
       <c r="I44" s="2" t="n">
-        <v>20.10861298155597</v>
+        <v>22.45536676768313</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>0.2217179951596117</v>
+        <v>0.3229788322979507</v>
       </c>
       <c r="K44" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L44" s="2" t="n">
         <v>0</v>
@@ -2796,31 +2796,31 @@
         <v>-1</v>
       </c>
       <c r="N44" s="2" t="n">
-        <v>-1.479757875029615</v>
+        <v>-0.1485687960909136</v>
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="n">
-        <v>9911</v>
+        <v>8088</v>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>櫻花</t>
+          <t>品安</t>
         </is>
       </c>
       <c r="C45" s="2" t="n">
         <v/>
       </c>
       <c r="D45" s="2" t="n">
-        <v>359.1427988272519</v>
+        <v>360.2063557022962</v>
       </c>
       <c r="E45" s="2" t="n">
-        <v>84.2</v>
+        <v>50.3</v>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
@@ -2831,16 +2831,16 @@
         <v>0</v>
       </c>
       <c r="H45" s="2" t="n">
-        <v>53.77869569438918</v>
+        <v>32.41050364806375</v>
       </c>
       <c r="I45" s="2" t="n">
-        <v>12.59852224685715</v>
+        <v>20.10861298155597</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>0.4724992219043894</v>
+        <v>0.2217179951596117</v>
       </c>
       <c r="K45" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L45" s="2" t="n">
         <v>0</v>
@@ -2849,31 +2849,31 @@
         <v>-1</v>
       </c>
       <c r="N45" s="2" t="n">
-        <v>0.0360394110733506</v>
+        <v>-1.479757875029615</v>
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="n">
-        <v>8443</v>
+        <v>9911</v>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>阿瘦</t>
+          <t>櫻花</t>
         </is>
       </c>
       <c r="C46" s="2" t="n">
         <v/>
       </c>
       <c r="D46" s="2" t="n">
-        <v>355.2401939905492</v>
+        <v>359.1427988272519</v>
       </c>
       <c r="E46" s="2" t="n">
-        <v>11.4</v>
+        <v>84.2</v>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
@@ -2884,13 +2884,13 @@
         <v>0</v>
       </c>
       <c r="H46" s="2" t="n">
-        <v>46.99881483791027</v>
+        <v>53.77869569438918</v>
       </c>
       <c r="I46" s="2" t="n">
-        <v>47.11996532976018</v>
+        <v>12.59852224685715</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>0.4064165532992746</v>
+        <v>0.4724992219043894</v>
       </c>
       <c r="K46" s="2" t="n">
         <v>0</v>
@@ -2902,31 +2902,31 @@
         <v>-1</v>
       </c>
       <c r="N46" s="2" t="n">
-        <v>-0.0059938638924886</v>
+        <v>0.0360394110733506</v>
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="n">
-        <v>8163</v>
+        <v>8443</v>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>達方</t>
+          <t>阿瘦</t>
         </is>
       </c>
       <c r="C47" s="2" t="n">
         <v/>
       </c>
       <c r="D47" s="2" t="n">
-        <v>355.2237274904185</v>
+        <v>355.2401939905492</v>
       </c>
       <c r="E47" s="2" t="n">
-        <v>35.35</v>
+        <v>11.4</v>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
@@ -2937,13 +2937,13 @@
         <v>0</v>
       </c>
       <c r="H47" s="2" t="n">
-        <v>38.84969898335167</v>
+        <v>46.99881483791027</v>
       </c>
       <c r="I47" s="2" t="n">
-        <v>24.62487872219254</v>
+        <v>47.11996532976018</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>0.2363060956230676</v>
+        <v>0.4064165532992746</v>
       </c>
       <c r="K47" s="2" t="n">
         <v>0</v>
@@ -2955,31 +2955,31 @@
         <v>-1</v>
       </c>
       <c r="N47" s="2" t="n">
-        <v>-0.9993737498204878</v>
+        <v>-0.0059938638924886</v>
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="n">
-        <v>8374</v>
+        <v>8163</v>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>羅昇</t>
+          <t>達方</t>
         </is>
       </c>
       <c r="C48" s="2" t="n">
         <v/>
       </c>
       <c r="D48" s="2" t="n">
-        <v>352.9214573128687</v>
+        <v>355.2237274904185</v>
       </c>
       <c r="E48" s="2" t="n">
-        <v>82.8</v>
+        <v>35.35</v>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
@@ -2990,13 +2990,13 @@
         <v>0</v>
       </c>
       <c r="H48" s="2" t="n">
-        <v>40.53066792221419</v>
+        <v>38.84969898335167</v>
       </c>
       <c r="I48" s="2" t="n">
-        <v>11.33412976012185</v>
+        <v>24.62487872219254</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>0.3174497259234393</v>
+        <v>0.2363060956230676</v>
       </c>
       <c r="K48" s="2" t="n">
         <v>0</v>
@@ -3008,31 +3008,31 @@
         <v>-1</v>
       </c>
       <c r="N48" s="2" t="n">
-        <v>-0.4411491855106453</v>
+        <v>-0.9993737498204878</v>
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="n">
-        <v>8499</v>
+        <v>8374</v>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>鼎炫-KY</t>
+          <t>羅昇</t>
         </is>
       </c>
       <c r="C49" s="2" t="n">
         <v/>
       </c>
       <c r="D49" s="2" t="n">
-        <v>351.3399906570308</v>
+        <v>352.9214573128687</v>
       </c>
       <c r="E49" s="2" t="n">
-        <v>292</v>
+        <v>82.8</v>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
@@ -3043,13 +3043,13 @@
         <v>0</v>
       </c>
       <c r="H49" s="2" t="n">
-        <v>47.18846448380247</v>
+        <v>40.53066792221419</v>
       </c>
       <c r="I49" s="2" t="n">
-        <v>12.0691246246748</v>
+        <v>11.33412976012185</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>0.332122526234654</v>
+        <v>0.3174497259234393</v>
       </c>
       <c r="K49" s="2" t="n">
         <v>0</v>
@@ -3061,31 +3061,31 @@
         <v>-1</v>
       </c>
       <c r="N49" s="2" t="n">
-        <v>-2.220822899882122</v>
+        <v>-0.4411491855106453</v>
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="n">
-        <v>8210</v>
+        <v>8499</v>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>勤誠</t>
+          <t>鼎炫-KY</t>
         </is>
       </c>
       <c r="C50" s="2" t="n">
         <v/>
       </c>
       <c r="D50" s="2" t="n">
-        <v>349.8299185250998</v>
+        <v>351.3399906570308</v>
       </c>
       <c r="E50" s="2" t="n">
-        <v>1175</v>
+        <v>292</v>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
@@ -3096,13 +3096,13 @@
         <v>0</v>
       </c>
       <c r="H50" s="2" t="n">
-        <v>41.16012271160109</v>
+        <v>47.18846448380247</v>
       </c>
       <c r="I50" s="2" t="n">
-        <v>21.63775721047337</v>
+        <v>12.0691246246748</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>0.8385518686468327</v>
+        <v>0.332122526234654</v>
       </c>
       <c r="K50" s="2" t="n">
         <v>0</v>
@@ -3114,31 +3114,31 @@
         <v>-1</v>
       </c>
       <c r="N50" s="2" t="n">
-        <v>-13.44713835237402</v>
+        <v>-2.220822899882122</v>
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="n">
-        <v>8390</v>
+        <v>8210</v>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>金益鼎</t>
+          <t>勤誠</t>
         </is>
       </c>
       <c r="C51" s="2" t="n">
         <v/>
       </c>
       <c r="D51" s="2" t="n">
-        <v>349.3941592490424</v>
+        <v>349.8299185250998</v>
       </c>
       <c r="E51" s="2" t="n">
-        <v>102.5</v>
+        <v>1175</v>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
@@ -3149,13 +3149,13 @@
         <v>0</v>
       </c>
       <c r="H51" s="2" t="n">
-        <v>41.36500832210614</v>
+        <v>41.16012271160109</v>
       </c>
       <c r="I51" s="2" t="n">
-        <v>22.8949756101772</v>
+        <v>21.63775721047337</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>0.6407723092691084</v>
+        <v>0.8385518686468327</v>
       </c>
       <c r="K51" s="2" t="n">
         <v>0</v>
@@ -3167,7 +3167,7 @@
         <v>-1</v>
       </c>
       <c r="N51" s="2" t="n">
-        <v>-0.5163232013958812</v>
+        <v>-13.44713835237402</v>
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
@@ -3177,21 +3177,21 @@
     </row>
     <row r="52">
       <c r="A52" s="2" t="n">
-        <v>8067</v>
+        <v>8390</v>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>志旭</t>
+          <t>金益鼎</t>
         </is>
       </c>
       <c r="C52" s="2" t="n">
         <v/>
       </c>
       <c r="D52" s="2" t="n">
-        <v>348.1640254752536</v>
+        <v>349.3941592490424</v>
       </c>
       <c r="E52" s="2" t="n">
-        <v>13.15</v>
+        <v>102.5</v>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
@@ -3202,13 +3202,13 @@
         <v>0</v>
       </c>
       <c r="H52" s="2" t="n">
-        <v>50.5855721663318</v>
+        <v>41.36500832210614</v>
       </c>
       <c r="I52" s="2" t="n">
-        <v>5.497454523027612</v>
+        <v>22.8949756101772</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>0.2200116352307093</v>
+        <v>0.6407723092691084</v>
       </c>
       <c r="K52" s="2" t="n">
         <v>0</v>
@@ -3220,31 +3220,31 @@
         <v>-1</v>
       </c>
       <c r="N52" s="2" t="n">
-        <v>-0.0725887634403858</v>
+        <v>-0.5163232013958812</v>
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="n">
-        <v>9105</v>
+        <v>8067</v>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>泰金寶-DR</t>
+          <t>志旭</t>
         </is>
       </c>
       <c r="C53" s="2" t="n">
         <v/>
       </c>
       <c r="D53" s="2" t="n">
-        <v>344.1427970384246</v>
+        <v>348.1640254752536</v>
       </c>
       <c r="E53" s="2" t="n">
-        <v>8.800000000000001</v>
+        <v>13.15</v>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
@@ -3255,13 +3255,13 @@
         <v>0</v>
       </c>
       <c r="H53" s="2" t="n">
-        <v>46.88153628407918</v>
+        <v>50.5855721663318</v>
       </c>
       <c r="I53" s="2" t="n">
-        <v>21.30385554815254</v>
+        <v>5.497454523027612</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>0.3374672353543567</v>
+        <v>0.2200116352307093</v>
       </c>
       <c r="K53" s="2" t="n">
         <v>0</v>
@@ -3273,31 +3273,31 @@
         <v>-1</v>
       </c>
       <c r="N53" s="2" t="n">
-        <v>-0.1280582754173493</v>
+        <v>-0.0725887634403858</v>
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="n">
-        <v>8114</v>
+        <v>9105</v>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>振樺電</t>
+          <t>泰金寶-DR</t>
         </is>
       </c>
       <c r="C54" s="2" t="n">
         <v/>
       </c>
       <c r="D54" s="2" t="n">
-        <v>340.5115195870458</v>
+        <v>344.1427970384246</v>
       </c>
       <c r="E54" s="2" t="n">
-        <v>194</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
@@ -3308,13 +3308,13 @@
         <v>0</v>
       </c>
       <c r="H54" s="2" t="n">
-        <v>42.78491000629568</v>
+        <v>46.88153628407918</v>
       </c>
       <c r="I54" s="2" t="n">
-        <v>16.31672930077571</v>
+        <v>21.30385554815254</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>0.2528431415336234</v>
+        <v>0.3374672353543567</v>
       </c>
       <c r="K54" s="2" t="n">
         <v>0</v>
@@ -3326,31 +3326,31 @@
         <v>-1</v>
       </c>
       <c r="N54" s="2" t="n">
-        <v>0.4713577624382195</v>
+        <v>-0.1280582754173493</v>
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="n">
-        <v>8473</v>
+        <v>8114</v>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>山林水</t>
+          <t>振樺電</t>
         </is>
       </c>
       <c r="C55" s="2" t="n">
         <v/>
       </c>
       <c r="D55" s="2" t="n">
-        <v>339.9749878529084</v>
+        <v>340.5115195870458</v>
       </c>
       <c r="E55" s="2" t="n">
-        <v>46.7</v>
+        <v>194</v>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
@@ -3361,13 +3361,13 @@
         <v>0</v>
       </c>
       <c r="H55" s="2" t="n">
-        <v>48.23040948640129</v>
+        <v>42.78491000629568</v>
       </c>
       <c r="I55" s="2" t="n">
-        <v>20.7739723382339</v>
+        <v>16.31672930077571</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>0.6963307546762582</v>
+        <v>0.2528431415336234</v>
       </c>
       <c r="K55" s="2" t="n">
         <v>0</v>
@@ -3379,31 +3379,31 @@
         <v>-1</v>
       </c>
       <c r="N55" s="2" t="n">
-        <v>-0.6009790813471042</v>
+        <v>0.4713577624382195</v>
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="n">
-        <v>8064</v>
+        <v>8473</v>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>東捷</t>
+          <t>山林水</t>
         </is>
       </c>
       <c r="C56" s="2" t="n">
         <v/>
       </c>
       <c r="D56" s="2" t="n">
-        <v>336.6876240100158</v>
+        <v>339.9749878529084</v>
       </c>
       <c r="E56" s="2" t="n">
-        <v>127.5</v>
+        <v>46.7</v>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
@@ -3414,16 +3414,16 @@
         <v>0</v>
       </c>
       <c r="H56" s="2" t="n">
-        <v>43.59398231120081</v>
+        <v>48.23040948640129</v>
       </c>
       <c r="I56" s="2" t="n">
-        <v>16.28178481414156</v>
+        <v>20.7739723382339</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>0.4151439403117416</v>
+        <v>0.6963307546762582</v>
       </c>
       <c r="K56" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L56" s="2" t="n">
         <v>0</v>
@@ -3432,31 +3432,31 @@
         <v>-1</v>
       </c>
       <c r="N56" s="2" t="n">
-        <v>-2.313485211780501</v>
+        <v>-0.6009790813471042</v>
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="n">
-        <v>8162</v>
+        <v>8064</v>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>微矽電子-創</t>
+          <t>東捷</t>
         </is>
       </c>
       <c r="C57" s="2" t="n">
         <v/>
       </c>
       <c r="D57" s="2" t="n">
-        <v>333.9435844300204</v>
+        <v>336.6876240100158</v>
       </c>
       <c r="E57" s="2" t="n">
-        <v>70.5</v>
+        <v>127.5</v>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
@@ -3467,16 +3467,16 @@
         <v>0</v>
       </c>
       <c r="H57" s="2" t="n">
-        <v>44.64917527216968</v>
+        <v>43.59398231120081</v>
       </c>
       <c r="I57" s="2" t="n">
-        <v>28.60729525606764</v>
+        <v>16.28178481414156</v>
       </c>
       <c r="J57" s="2" t="n">
-        <v>0.2029362719892403</v>
+        <v>0.4151439403117416</v>
       </c>
       <c r="K57" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L57" s="2" t="n">
         <v>0</v>
@@ -3485,31 +3485,31 @@
         <v>-1</v>
       </c>
       <c r="N57" s="2" t="n">
-        <v>-1.90657022896781</v>
+        <v>-2.313485211780501</v>
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="n">
-        <v>8069</v>
+        <v>8162</v>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>元太</t>
+          <t>微矽電子-創</t>
         </is>
       </c>
       <c r="C58" s="2" t="n">
         <v/>
       </c>
       <c r="D58" s="2" t="n">
-        <v>328.927707697279</v>
+        <v>333.9435844300204</v>
       </c>
       <c r="E58" s="2" t="n">
-        <v>184</v>
+        <v>70.5</v>
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
@@ -3520,49 +3520,49 @@
         <v>0</v>
       </c>
       <c r="H58" s="2" t="n">
-        <v>38.01681349125182</v>
+        <v>44.64917527216968</v>
       </c>
       <c r="I58" s="2" t="n">
-        <v>16.05652685517753</v>
+        <v>28.60729525606764</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>0.6863922871522035</v>
+        <v>0.2029362719892403</v>
       </c>
       <c r="K58" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L58" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M58" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N58" s="2" t="n">
-        <v>-2.245366534895879</v>
+        <v>-1.90657022896781</v>
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="n">
-        <v>8455</v>
+        <v>8069</v>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>大拓-KY</t>
+          <t>元太</t>
         </is>
       </c>
       <c r="C59" s="2" t="n">
         <v/>
       </c>
       <c r="D59" s="2" t="n">
-        <v>327.0315958096689</v>
+        <v>328.927707697279</v>
       </c>
       <c r="E59" s="2" t="n">
-        <v>27</v>
+        <v>184</v>
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
@@ -3573,49 +3573,49 @@
         <v>0</v>
       </c>
       <c r="H59" s="2" t="n">
-        <v>43.49591416431616</v>
+        <v>38.01681349125182</v>
       </c>
       <c r="I59" s="2" t="n">
-        <v>19.52309048970485</v>
+        <v>16.05652685517753</v>
       </c>
       <c r="J59" s="2" t="n">
-        <v>0.4981897247443773</v>
+        <v>0.6863922871522035</v>
       </c>
       <c r="K59" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L59" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M59" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N59" s="2" t="n">
-        <v>-0.0218068517413141</v>
+        <v>-2.245366534895879</v>
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross, williams_r_recovery</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="n">
-        <v>8176</v>
+        <v>8455</v>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>智捷</t>
+          <t>大拓-KY</t>
         </is>
       </c>
       <c r="C60" s="2" t="n">
         <v/>
       </c>
       <c r="D60" s="2" t="n">
-        <v>326.2072613265802</v>
+        <v>327.0315958096689</v>
       </c>
       <c r="E60" s="2" t="n">
-        <v>10.2</v>
+        <v>27</v>
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
@@ -3626,16 +3626,16 @@
         <v>0</v>
       </c>
       <c r="H60" s="2" t="n">
-        <v>48.24961573123961</v>
+        <v>43.49591416431616</v>
       </c>
       <c r="I60" s="2" t="n">
-        <v>19.88305164872468</v>
+        <v>19.52309048970485</v>
       </c>
       <c r="J60" s="2" t="n">
-        <v>0.295435602909168</v>
+        <v>0.4981897247443773</v>
       </c>
       <c r="K60" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L60" s="2" t="n">
         <v>0</v>
@@ -3644,31 +3644,31 @@
         <v>-1</v>
       </c>
       <c r="N60" s="2" t="n">
-        <v>-0.0249349422806728</v>
+        <v>-0.0218068517413141</v>
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, foreign_buy_3d, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross, williams_r_recovery</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="n">
-        <v>8084</v>
+        <v>8176</v>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>巨虹</t>
+          <t>智捷</t>
         </is>
       </c>
       <c r="C61" s="2" t="n">
         <v/>
       </c>
       <c r="D61" s="2" t="n">
-        <v>323.6908150222484</v>
+        <v>326.2072613265802</v>
       </c>
       <c r="E61" s="2" t="n">
-        <v>46</v>
+        <v>10.2</v>
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
@@ -3679,16 +3679,16 @@
         <v>0</v>
       </c>
       <c r="H61" s="2" t="n">
-        <v>43.81498927365324</v>
+        <v>48.24961573123961</v>
       </c>
       <c r="I61" s="2" t="n">
-        <v>19.54085266487287</v>
+        <v>19.88305164872468</v>
       </c>
       <c r="J61" s="2" t="n">
-        <v>2.249883091814957</v>
+        <v>0.295435602909168</v>
       </c>
       <c r="K61" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L61" s="2" t="n">
         <v>0</v>
@@ -3697,31 +3697,31 @@
         <v>-1</v>
       </c>
       <c r="N61" s="2" t="n">
-        <v>-0.5590481756393466</v>
+        <v>-0.0249349422806728</v>
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="n">
-        <v>8454</v>
+        <v>8084</v>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>富邦媒</t>
+          <t>巨虹</t>
         </is>
       </c>
       <c r="C62" s="2" t="n">
         <v/>
       </c>
       <c r="D62" s="2" t="n">
-        <v>315.407500843627</v>
+        <v>323.6908150222484</v>
       </c>
       <c r="E62" s="2" t="n">
-        <v>267.5</v>
+        <v>46</v>
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
@@ -3732,16 +3732,16 @@
         <v>0</v>
       </c>
       <c r="H62" s="2" t="n">
-        <v>43.1975848399147</v>
+        <v>43.81498927365324</v>
       </c>
       <c r="I62" s="2" t="n">
-        <v>23.33012285594128</v>
+        <v>19.54085266487287</v>
       </c>
       <c r="J62" s="2" t="n">
-        <v>0.3453194471031168</v>
+        <v>2.249883091814957</v>
       </c>
       <c r="K62" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L62" s="2" t="n">
         <v>0</v>
@@ -3750,31 +3750,31 @@
         <v>-1</v>
       </c>
       <c r="N62" s="2" t="n">
-        <v>-7.007094641453925</v>
+        <v>-0.5590481756393466</v>
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
+          <t>volume_break, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="n">
-        <v>8478</v>
+        <v>8454</v>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>東哥遊艇</t>
+          <t>富邦媒</t>
         </is>
       </c>
       <c r="C63" s="2" t="n">
         <v/>
       </c>
       <c r="D63" s="2" t="n">
-        <v>306.3662029876388</v>
+        <v>315.407500843627</v>
       </c>
       <c r="E63" s="2" t="n">
-        <v>155.5</v>
+        <v>267.5</v>
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
@@ -3785,13 +3785,13 @@
         <v>0</v>
       </c>
       <c r="H63" s="2" t="n">
-        <v>50.30689566811357</v>
+        <v>43.1975848399147</v>
       </c>
       <c r="I63" s="2" t="n">
-        <v>17.5241994678118</v>
+        <v>23.33012285594128</v>
       </c>
       <c r="J63" s="2" t="n">
-        <v>0.2904905887381468</v>
+        <v>0.3453194471031168</v>
       </c>
       <c r="K63" s="2" t="n">
         <v>0</v>
@@ -3803,31 +3803,31 @@
         <v>-1</v>
       </c>
       <c r="N63" s="2" t="n">
-        <v>0.3242080517494368</v>
+        <v>-7.007094641453925</v>
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="n">
-        <v>8404</v>
+        <v>8291</v>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>百和興業-KY</t>
+          <t>尚茂</t>
         </is>
       </c>
       <c r="C64" s="2" t="n">
         <v/>
       </c>
       <c r="D64" s="2" t="n">
-        <v>305.9062713333718</v>
+        <v>307.942087978222</v>
       </c>
       <c r="E64" s="2" t="n">
-        <v>17.05</v>
+        <v>27.35</v>
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
@@ -3838,13 +3838,13 @@
         <v>0</v>
       </c>
       <c r="H64" s="2" t="n">
-        <v>54.88940986947985</v>
+        <v>31.90079639629977</v>
       </c>
       <c r="I64" s="2" t="n">
-        <v>18.50883634711758</v>
+        <v>32.39035546822535</v>
       </c>
       <c r="J64" s="2" t="n">
-        <v>1.215397959667282</v>
+        <v>0.2684038707238921</v>
       </c>
       <c r="K64" s="2" t="n">
         <v>0</v>
@@ -3856,31 +3856,31 @@
         <v>-1</v>
       </c>
       <c r="N64" s="2" t="n">
-        <v>0.0589130348510811</v>
+        <v>-0.8871402107968818</v>
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="n">
-        <v>8101</v>
+        <v>8478</v>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>華冠</t>
+          <t>東哥遊艇</t>
         </is>
       </c>
       <c r="C65" s="2" t="n">
         <v/>
       </c>
       <c r="D65" s="2" t="n">
-        <v>298.8121765472105</v>
+        <v>306.3662029876388</v>
       </c>
       <c r="E65" s="2" t="n">
-        <v>13.4</v>
+        <v>155.5</v>
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
@@ -3891,13 +3891,13 @@
         <v>0</v>
       </c>
       <c r="H65" s="2" t="n">
-        <v>47.3939371873141</v>
+        <v>50.30689566811357</v>
       </c>
       <c r="I65" s="2" t="n">
-        <v>11.54533090381199</v>
+        <v>17.5241994678118</v>
       </c>
       <c r="J65" s="2" t="n">
-        <v>12.88693279631013</v>
+        <v>0.2904905887381468</v>
       </c>
       <c r="K65" s="2" t="n">
         <v>0</v>
@@ -3909,31 +3909,31 @@
         <v>-1</v>
       </c>
       <c r="N65" s="2" t="n">
-        <v>-0.0013080677730851</v>
+        <v>0.3242080517494368</v>
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="n">
-        <v>8299</v>
+        <v>8404</v>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>群聯</t>
+          <t>百和興業-KY</t>
         </is>
       </c>
       <c r="C66" s="2" t="n">
         <v/>
       </c>
       <c r="D66" s="2" t="n">
-        <v>298.0107066805257</v>
+        <v>305.9062713333718</v>
       </c>
       <c r="E66" s="2" t="n">
-        <v>1980</v>
+        <v>17.05</v>
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
@@ -3944,13 +3944,13 @@
         <v>0</v>
       </c>
       <c r="H66" s="2" t="n">
-        <v>36.99373356835566</v>
+        <v>54.88940986947985</v>
       </c>
       <c r="I66" s="2" t="n">
-        <v>14.40048808011118</v>
+        <v>18.50883634711758</v>
       </c>
       <c r="J66" s="2" t="n">
-        <v>1.084526331711917</v>
+        <v>1.215397959667282</v>
       </c>
       <c r="K66" s="2" t="n">
         <v>0</v>
@@ -3962,31 +3962,31 @@
         <v>-1</v>
       </c>
       <c r="N66" s="2" t="n">
-        <v>-32.57541805814127</v>
+        <v>0.0589130348510811</v>
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="n">
-        <v>8171</v>
+        <v>8101</v>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>天宇</t>
+          <t>華冠</t>
         </is>
       </c>
       <c r="C67" s="2" t="n">
         <v/>
       </c>
       <c r="D67" s="2" t="n">
-        <v>294.3253947471331</v>
+        <v>298.8121765472105</v>
       </c>
       <c r="E67" s="2" t="n">
-        <v>20.5</v>
+        <v>13.4</v>
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
@@ -3997,16 +3997,16 @@
         <v>0</v>
       </c>
       <c r="H67" s="2" t="n">
-        <v>40.97395958866276</v>
+        <v>47.3939371873141</v>
       </c>
       <c r="I67" s="2" t="n">
-        <v>17.28571969261858</v>
+        <v>11.54533090381199</v>
       </c>
       <c r="J67" s="2" t="n">
-        <v>0.6129177395121462</v>
+        <v>12.88693279631013</v>
       </c>
       <c r="K67" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L67" s="2" t="n">
         <v>0</v>
@@ -4015,31 +4015,31 @@
         <v>-1</v>
       </c>
       <c r="N67" s="2" t="n">
-        <v>0.0136111248375259</v>
+        <v>-0.0013080677730851</v>
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, market_above_ma60, avoid_chase, hist_turn_positive</t>
+          <t>volume_break, market_above_ma60, avoid_chase, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="n">
-        <v>8996</v>
+        <v>8299</v>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>高力</t>
+          <t>群聯</t>
         </is>
       </c>
       <c r="C68" s="2" t="n">
         <v/>
       </c>
       <c r="D68" s="2" t="n">
-        <v>293.3130732281733</v>
+        <v>298.0107066805257</v>
       </c>
       <c r="E68" s="2" t="n">
-        <v>1125</v>
+        <v>1980</v>
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
@@ -4050,13 +4050,13 @@
         <v>0</v>
       </c>
       <c r="H68" s="2" t="n">
-        <v>38.37652437455209</v>
+        <v>36.99373356835566</v>
       </c>
       <c r="I68" s="2" t="n">
-        <v>19.91705535739804</v>
+        <v>14.40048808011118</v>
       </c>
       <c r="J68" s="2" t="n">
-        <v>0.6198671796429434</v>
+        <v>1.084526331711917</v>
       </c>
       <c r="K68" s="2" t="n">
         <v>0</v>
@@ -4068,7 +4068,7 @@
         <v>-1</v>
       </c>
       <c r="N68" s="2" t="n">
-        <v>-45.69969092931599</v>
+        <v>-32.57541805814127</v>
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
@@ -4078,21 +4078,21 @@
     </row>
     <row r="69">
       <c r="A69" s="2" t="n">
-        <v>8358</v>
+        <v>8171</v>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>金居</t>
+          <t>天宇</t>
         </is>
       </c>
       <c r="C69" s="2" t="n">
         <v/>
       </c>
       <c r="D69" s="2" t="n">
-        <v>289.9175817870945</v>
+        <v>294.3253947471331</v>
       </c>
       <c r="E69" s="2" t="n">
-        <v>439</v>
+        <v>20.5</v>
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
@@ -4103,16 +4103,16 @@
         <v>0</v>
       </c>
       <c r="H69" s="2" t="n">
-        <v>33.99345752535061</v>
+        <v>40.97395958866276</v>
       </c>
       <c r="I69" s="2" t="n">
-        <v>15.1409821978877</v>
+        <v>17.28571969261858</v>
       </c>
       <c r="J69" s="2" t="n">
-        <v>0.4405645380506977</v>
+        <v>0.6129177395121462</v>
       </c>
       <c r="K69" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L69" s="2" t="n">
         <v>0</v>
@@ -4121,31 +4121,31 @@
         <v>-1</v>
       </c>
       <c r="N69" s="2" t="n">
-        <v>-20.05791919581365</v>
+        <v>0.0136111248375259</v>
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>macd_golden_cross, market_above_ma60, avoid_chase, hist_turn_positive</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="n">
-        <v>8086</v>
+        <v>8996</v>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>宏捷科</t>
+          <t>高力</t>
         </is>
       </c>
       <c r="C70" s="2" t="n">
         <v/>
       </c>
       <c r="D70" s="2" t="n">
-        <v>281.2041938659735</v>
+        <v>293.3130732281733</v>
       </c>
       <c r="E70" s="2" t="n">
-        <v>127</v>
+        <v>1125</v>
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
@@ -4156,25 +4156,25 @@
         <v>0</v>
       </c>
       <c r="H70" s="2" t="n">
-        <v>34.68062729184621</v>
+        <v>38.37652437455209</v>
       </c>
       <c r="I70" s="2" t="n">
-        <v>17.76542606529004</v>
+        <v>19.91705535739804</v>
       </c>
       <c r="J70" s="2" t="n">
-        <v>0.453778761093887</v>
+        <v>0.6198671796429434</v>
       </c>
       <c r="K70" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L70" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M70" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N70" s="2" t="n">
-        <v>-1.802169785909165</v>
+        <v>-45.69969092931599</v>
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
@@ -4184,21 +4184,21 @@
     </row>
     <row r="71">
       <c r="A71" s="2" t="n">
-        <v>8104</v>
+        <v>8358</v>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>錸寶</t>
+          <t>金居</t>
         </is>
       </c>
       <c r="C71" s="2" t="n">
         <v/>
       </c>
       <c r="D71" s="2" t="n">
-        <v>277.4576281903288</v>
+        <v>289.9175817870945</v>
       </c>
       <c r="E71" s="2" t="n">
-        <v>37.1</v>
+        <v>439</v>
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
@@ -4209,16 +4209,16 @@
         <v>0</v>
       </c>
       <c r="H71" s="2" t="n">
-        <v>42.78400298476919</v>
+        <v>33.99345752535061</v>
       </c>
       <c r="I71" s="2" t="n">
-        <v>17.67125464773972</v>
+        <v>15.1409821978877</v>
       </c>
       <c r="J71" s="2" t="n">
-        <v>0.2250441290388535</v>
+        <v>0.4405645380506977</v>
       </c>
       <c r="K71" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L71" s="2" t="n">
         <v>0</v>
@@ -4227,31 +4227,31 @@
         <v>-1</v>
       </c>
       <c r="N71" s="2" t="n">
-        <v>-0.2546206303762283</v>
+        <v>-20.05791919581365</v>
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="n">
-        <v>8440</v>
+        <v>8086</v>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>綠電</t>
+          <t>宏捷科</t>
         </is>
       </c>
       <c r="C72" s="2" t="n">
         <v/>
       </c>
       <c r="D72" s="2" t="n">
-        <v>276.6892003830151</v>
+        <v>281.2041938659735</v>
       </c>
       <c r="E72" s="2" t="n">
-        <v>20.75</v>
+        <v>127</v>
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
@@ -4262,49 +4262,49 @@
         <v>0</v>
       </c>
       <c r="H72" s="2" t="n">
-        <v>37.71952018439433</v>
+        <v>34.68062729184621</v>
       </c>
       <c r="I72" s="2" t="n">
-        <v>10.23098885902727</v>
+        <v>17.76542606529004</v>
       </c>
       <c r="J72" s="2" t="n">
-        <v>0.9310147350459594</v>
+        <v>0.453778761093887</v>
       </c>
       <c r="K72" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L72" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M72" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N72" s="2" t="n">
-        <v>-0.0547049479375932</v>
+        <v>-1.802169785909165</v>
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, dealer_buy_3d</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="n">
-        <v>8112</v>
+        <v>8104</v>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>至上</t>
+          <t>錸寶</t>
         </is>
       </c>
       <c r="C73" s="2" t="n">
         <v/>
       </c>
       <c r="D73" s="2" t="n">
-        <v>275.8929276960484</v>
+        <v>277.4576281903288</v>
       </c>
       <c r="E73" s="2" t="n">
-        <v>85.8</v>
+        <v>37.1</v>
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
@@ -4315,13 +4315,13 @@
         <v>0</v>
       </c>
       <c r="H73" s="2" t="n">
-        <v>42.95593475300067</v>
+        <v>42.78400298476919</v>
       </c>
       <c r="I73" s="2" t="n">
-        <v>13.87021181619469</v>
+        <v>17.67125464773972</v>
       </c>
       <c r="J73" s="2" t="n">
-        <v>0.4578607871526183</v>
+        <v>0.2250441290388535</v>
       </c>
       <c r="K73" s="2" t="n">
         <v>0</v>
@@ -4333,31 +4333,31 @@
         <v>-1</v>
       </c>
       <c r="N73" s="2" t="n">
-        <v>-0.8483000195552353</v>
+        <v>-0.2546206303762283</v>
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="n">
-        <v>8110</v>
+        <v>8440</v>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>華東</t>
+          <t>綠電</t>
         </is>
       </c>
       <c r="C74" s="2" t="n">
         <v/>
       </c>
       <c r="D74" s="2" t="n">
-        <v>273.4181020752116</v>
+        <v>276.6892003830151</v>
       </c>
       <c r="E74" s="2" t="n">
-        <v>47.8</v>
+        <v>20.75</v>
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
@@ -4368,16 +4368,16 @@
         <v>0</v>
       </c>
       <c r="H74" s="2" t="n">
-        <v>38.75974325630919</v>
+        <v>37.71952018439433</v>
       </c>
       <c r="I74" s="2" t="n">
-        <v>15.31016058361169</v>
+        <v>10.23098885902727</v>
       </c>
       <c r="J74" s="2" t="n">
-        <v>0.3030467951503547</v>
+        <v>0.9310147350459594</v>
       </c>
       <c r="K74" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L74" s="2" t="n">
         <v>0</v>
@@ -4386,31 +4386,31 @@
         <v>-1</v>
       </c>
       <c r="N74" s="2" t="n">
-        <v>-0.9353157149891402</v>
+        <v>-0.0547049479375932</v>
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>market_above_ma60, avoid_chase, dealer_buy_3d</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="n">
-        <v>8070</v>
+        <v>8112</v>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>長華*</t>
+          <t>至上</t>
         </is>
       </c>
       <c r="C75" s="2" t="n">
         <v/>
       </c>
       <c r="D75" s="2" t="n">
-        <v>272.7906792016488</v>
+        <v>275.8929276960484</v>
       </c>
       <c r="E75" s="2" t="n">
-        <v>51.2</v>
+        <v>85.8</v>
       </c>
       <c r="F75" s="2" t="inlineStr">
         <is>
@@ -4421,13 +4421,13 @@
         <v>0</v>
       </c>
       <c r="H75" s="2" t="n">
-        <v>42.71736339180384</v>
+        <v>42.95593475300067</v>
       </c>
       <c r="I75" s="2" t="n">
-        <v>18.02165734278453</v>
+        <v>13.87021181619469</v>
       </c>
       <c r="J75" s="2" t="n">
-        <v>0.4531053643281004</v>
+        <v>0.4578607871526183</v>
       </c>
       <c r="K75" s="2" t="n">
         <v>0</v>
@@ -4439,7 +4439,7 @@
         <v>-1</v>
       </c>
       <c r="N75" s="2" t="n">
-        <v>-0.6725517491090949</v>
+        <v>-0.8483000195552353</v>
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
@@ -4449,21 +4449,21 @@
     </row>
     <row r="76">
       <c r="A76" s="2" t="n">
-        <v>8215</v>
+        <v>8110</v>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>明基材</t>
+          <t>華東</t>
         </is>
       </c>
       <c r="C76" s="2" t="n">
         <v/>
       </c>
       <c r="D76" s="2" t="n">
-        <v>271.7010218759808</v>
+        <v>273.4181020752116</v>
       </c>
       <c r="E76" s="2" t="n">
-        <v>27.15</v>
+        <v>47.8</v>
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
@@ -4474,13 +4474,13 @@
         <v>0</v>
       </c>
       <c r="H76" s="2" t="n">
-        <v>42.90925056710768</v>
+        <v>38.75974325630919</v>
       </c>
       <c r="I76" s="2" t="n">
-        <v>18.40423118327642</v>
+        <v>15.31016058361169</v>
       </c>
       <c r="J76" s="2" t="n">
-        <v>0.1748086262854274</v>
+        <v>0.3030467951503547</v>
       </c>
       <c r="K76" s="2" t="n">
         <v>0</v>
@@ -4492,7 +4492,7 @@
         <v>-1</v>
       </c>
       <c r="N76" s="2" t="n">
-        <v>-0.3511248460149315</v>
+        <v>-0.9353157149891402</v>
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
@@ -4502,21 +4502,21 @@
     </row>
     <row r="77">
       <c r="A77" s="2" t="n">
-        <v>8240</v>
+        <v>8070</v>
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>華宏</t>
+          <t>長華*</t>
         </is>
       </c>
       <c r="C77" s="2" t="n">
         <v/>
       </c>
       <c r="D77" s="2" t="n">
-        <v>268.8002422759964</v>
+        <v>272.7906792016488</v>
       </c>
       <c r="E77" s="2" t="n">
-        <v>46.3</v>
+        <v>51.2</v>
       </c>
       <c r="F77" s="2" t="inlineStr">
         <is>
@@ -4527,13 +4527,13 @@
         <v>0</v>
       </c>
       <c r="H77" s="2" t="n">
-        <v>31.53342321174729</v>
+        <v>42.71736339180384</v>
       </c>
       <c r="I77" s="2" t="n">
-        <v>22.53871354139675</v>
+        <v>18.02165734278453</v>
       </c>
       <c r="J77" s="2" t="n">
-        <v>0.2965107865712923</v>
+        <v>0.4531053643281004</v>
       </c>
       <c r="K77" s="2" t="n">
         <v>0</v>
@@ -4545,31 +4545,31 @@
         <v>-1</v>
       </c>
       <c r="N77" s="2" t="n">
-        <v>-0.323826927904733</v>
+        <v>-0.6725517491090949</v>
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="n">
-        <v>8049</v>
+        <v>8215</v>
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>晶采</t>
+          <t>明基材</t>
         </is>
       </c>
       <c r="C78" s="2" t="n">
         <v/>
       </c>
       <c r="D78" s="2" t="n">
-        <v>268.644019389408</v>
+        <v>271.7010218759808</v>
       </c>
       <c r="E78" s="2" t="n">
-        <v>26.4</v>
+        <v>27.15</v>
       </c>
       <c r="F78" s="2" t="inlineStr">
         <is>
@@ -4580,13 +4580,13 @@
         <v>0</v>
       </c>
       <c r="H78" s="2" t="n">
-        <v>43.1312941828502</v>
+        <v>42.90925056710768</v>
       </c>
       <c r="I78" s="2" t="n">
-        <v>19.74693472828664</v>
+        <v>18.40423118327642</v>
       </c>
       <c r="J78" s="2" t="n">
-        <v>0.3147161729388533</v>
+        <v>0.1748086262854274</v>
       </c>
       <c r="K78" s="2" t="n">
         <v>0</v>
@@ -4598,31 +4598,31 @@
         <v>-1</v>
       </c>
       <c r="N78" s="2" t="n">
-        <v>-0.1433752696565288</v>
+        <v>-0.3511248460149315</v>
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="n">
-        <v>8111</v>
+        <v>8240</v>
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>立碁</t>
+          <t>華宏</t>
         </is>
       </c>
       <c r="C79" s="2" t="n">
         <v/>
       </c>
       <c r="D79" s="2" t="n">
-        <v>258.6966125492046</v>
+        <v>268.8002422759964</v>
       </c>
       <c r="E79" s="2" t="n">
-        <v>49.5</v>
+        <v>46.3</v>
       </c>
       <c r="F79" s="2" t="inlineStr">
         <is>
@@ -4633,13 +4633,13 @@
         <v>0</v>
       </c>
       <c r="H79" s="2" t="n">
-        <v>37.75318649764575</v>
+        <v>31.53342321174729</v>
       </c>
       <c r="I79" s="2" t="n">
-        <v>24.26556812946887</v>
+        <v>22.53871354139675</v>
       </c>
       <c r="J79" s="2" t="n">
-        <v>0.93743636697691</v>
+        <v>0.2965107865712923</v>
       </c>
       <c r="K79" s="2" t="n">
         <v>0</v>
@@ -4651,31 +4651,31 @@
         <v>-1</v>
       </c>
       <c r="N79" s="2" t="n">
-        <v>0.0788226162315335</v>
+        <v>-0.323826927904733</v>
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="n">
-        <v>8089</v>
+        <v>8049</v>
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>康全電訊</t>
+          <t>晶采</t>
         </is>
       </c>
       <c r="C80" s="2" t="n">
         <v/>
       </c>
       <c r="D80" s="2" t="n">
-        <v>243.9834763987312</v>
+        <v>268.644019389408</v>
       </c>
       <c r="E80" s="2" t="n">
-        <v>19.3</v>
+        <v>26.4</v>
       </c>
       <c r="F80" s="2" t="inlineStr">
         <is>
@@ -4686,13 +4686,13 @@
         <v>0</v>
       </c>
       <c r="H80" s="2" t="n">
-        <v>40.49199017279144</v>
+        <v>43.1312941828502</v>
       </c>
       <c r="I80" s="2" t="n">
-        <v>23.80352744719987</v>
+        <v>19.74693472828664</v>
       </c>
       <c r="J80" s="2" t="n">
-        <v>0.4329544789360898</v>
+        <v>0.3147161729388533</v>
       </c>
       <c r="K80" s="2" t="n">
         <v>0</v>
@@ -4704,31 +4704,31 @@
         <v>-1</v>
       </c>
       <c r="N80" s="2" t="n">
-        <v>-0.0976062415659695</v>
+        <v>-0.1433752696565288</v>
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="n">
-        <v>8201</v>
+        <v>8111</v>
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>無敵</t>
+          <t>立碁</t>
         </is>
       </c>
       <c r="C81" s="2" t="n">
         <v/>
       </c>
       <c r="D81" s="2" t="n">
-        <v>242.9448283082402</v>
+        <v>258.6966125492046</v>
       </c>
       <c r="E81" s="2" t="n">
-        <v>12.65</v>
+        <v>49.5</v>
       </c>
       <c r="F81" s="2" t="inlineStr">
         <is>
@@ -4739,13 +4739,13 @@
         <v>0</v>
       </c>
       <c r="H81" s="2" t="n">
-        <v>43.86534892821641</v>
+        <v>37.75318649764575</v>
       </c>
       <c r="I81" s="2" t="n">
-        <v>13.4570207743837</v>
+        <v>24.26556812946887</v>
       </c>
       <c r="J81" s="2" t="n">
-        <v>1.394804072632102</v>
+        <v>0.93743636697691</v>
       </c>
       <c r="K81" s="2" t="n">
         <v>0</v>
@@ -4757,31 +4757,31 @@
         <v>-1</v>
       </c>
       <c r="N81" s="2" t="n">
-        <v>-0.0555093448050608</v>
+        <v>0.0788226162315335</v>
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="n">
-        <v>9904</v>
+        <v>8089</v>
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>寶成</t>
+          <t>康全電訊</t>
         </is>
       </c>
       <c r="C82" s="2" t="n">
         <v/>
       </c>
       <c r="D82" s="2" t="n">
-        <v>230.4728153868459</v>
+        <v>243.9834763987312</v>
       </c>
       <c r="E82" s="2" t="n">
-        <v>24.6</v>
+        <v>19.3</v>
       </c>
       <c r="F82" s="2" t="inlineStr">
         <is>
@@ -4792,13 +4792,13 @@
         <v>0</v>
       </c>
       <c r="H82" s="2" t="n">
-        <v>40.95727844648801</v>
+        <v>40.49199017279144</v>
       </c>
       <c r="I82" s="2" t="n">
-        <v>24.05732452097143</v>
+        <v>23.80352744719987</v>
       </c>
       <c r="J82" s="2" t="n">
-        <v>1.364027321289888</v>
+        <v>0.4329544789360898</v>
       </c>
       <c r="K82" s="2" t="n">
         <v>0</v>
@@ -4810,31 +4810,31 @@
         <v>-1</v>
       </c>
       <c r="N82" s="2" t="n">
-        <v>-0.0260617562019949</v>
+        <v>-0.0976062415659695</v>
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="n">
-        <v>9906</v>
+        <v>8201</v>
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>欣巴巴</t>
+          <t>無敵</t>
         </is>
       </c>
       <c r="C83" s="2" t="n">
         <v/>
       </c>
       <c r="D83" s="2" t="n">
-        <v>227.7154376119349</v>
+        <v>242.9448283082402</v>
       </c>
       <c r="E83" s="2" t="n">
-        <v>41.6</v>
+        <v>12.65</v>
       </c>
       <c r="F83" s="2" t="inlineStr">
         <is>
@@ -4845,13 +4845,13 @@
         <v>0</v>
       </c>
       <c r="H83" s="2" t="n">
-        <v>51.88546289871752</v>
+        <v>43.86534892821641</v>
       </c>
       <c r="I83" s="2" t="n">
-        <v>24.84252536272482</v>
+        <v>13.4570207743837</v>
       </c>
       <c r="J83" s="2" t="n">
-        <v>0.4097183165065268</v>
+        <v>1.394804072632102</v>
       </c>
       <c r="K83" s="2" t="n">
         <v>0</v>
@@ -4863,31 +4863,31 @@
         <v>-1</v>
       </c>
       <c r="N83" s="2" t="n">
-        <v>-0.3145253371952038</v>
+        <v>-0.0555093448050608</v>
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="n">
-        <v>8059</v>
+        <v>9904</v>
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>凱碩</t>
+          <t>寶成</t>
         </is>
       </c>
       <c r="C84" s="2" t="n">
         <v/>
       </c>
       <c r="D84" s="2" t="n">
-        <v>227.1706502877066</v>
+        <v>230.4728153868459</v>
       </c>
       <c r="E84" s="2" t="n">
-        <v>16.6</v>
+        <v>24.6</v>
       </c>
       <c r="F84" s="2" t="inlineStr">
         <is>
@@ -4898,16 +4898,16 @@
         <v>0</v>
       </c>
       <c r="H84" s="2" t="n">
-        <v>44.51388320443243</v>
+        <v>40.95727844648801</v>
       </c>
       <c r="I84" s="2" t="n">
-        <v>21.0503042244405</v>
+        <v>24.05732452097143</v>
       </c>
       <c r="J84" s="2" t="n">
-        <v>0.6371354114109991</v>
+        <v>1.364027321289888</v>
       </c>
       <c r="K84" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L84" s="2" t="n">
         <v>0</v>
@@ -4916,31 +4916,31 @@
         <v>-1</v>
       </c>
       <c r="N84" s="2" t="n">
-        <v>0.1328674765799011</v>
+        <v>-0.0260617562019949</v>
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="n">
-        <v>9910</v>
+        <v>9906</v>
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>豐泰</t>
+          <t>欣巴巴</t>
         </is>
       </c>
       <c r="C85" s="2" t="n">
         <v/>
       </c>
       <c r="D85" s="2" t="n">
-        <v>225.9460424244129</v>
+        <v>227.7154376119349</v>
       </c>
       <c r="E85" s="2" t="n">
-        <v>67.8</v>
+        <v>41.6</v>
       </c>
       <c r="F85" s="2" t="inlineStr">
         <is>
@@ -4951,13 +4951,13 @@
         <v>0</v>
       </c>
       <c r="H85" s="2" t="n">
-        <v>41.89948994859546</v>
+        <v>51.88546289871752</v>
       </c>
       <c r="I85" s="2" t="n">
-        <v>18.81065289962456</v>
+        <v>24.84252536272482</v>
       </c>
       <c r="J85" s="2" t="n">
-        <v>0.3303295608426863</v>
+        <v>0.4097183165065268</v>
       </c>
       <c r="K85" s="2" t="n">
         <v>0</v>
@@ -4969,31 +4969,31 @@
         <v>-1</v>
       </c>
       <c r="N85" s="2" t="n">
-        <v>-0.1382559520683939</v>
+        <v>-0.3145253371952038</v>
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="n">
-        <v>8940</v>
+        <v>8059</v>
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>新天地</t>
+          <t>凱碩</t>
         </is>
       </c>
       <c r="C86" s="2" t="n">
         <v/>
       </c>
       <c r="D86" s="2" t="n">
-        <v>224.0716528109438</v>
+        <v>227.1706502877066</v>
       </c>
       <c r="E86" s="2" t="n">
-        <v>16.25</v>
+        <v>16.6</v>
       </c>
       <c r="F86" s="2" t="inlineStr">
         <is>
@@ -5004,16 +5004,16 @@
         <v>0</v>
       </c>
       <c r="H86" s="2" t="n">
-        <v>41.47253265756475</v>
+        <v>44.51388320443243</v>
       </c>
       <c r="I86" s="2" t="n">
-        <v>19.11107886224</v>
+        <v>21.0503042244405</v>
       </c>
       <c r="J86" s="2" t="n">
-        <v>0.5782847551515361</v>
+        <v>0.6371354114109991</v>
       </c>
       <c r="K86" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L86" s="2" t="n">
         <v>0</v>
@@ -5022,31 +5022,31 @@
         <v>-1</v>
       </c>
       <c r="N86" s="2" t="n">
-        <v>-0.0122274209931299</v>
+        <v>0.1328674765799011</v>
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="n">
-        <v>8048</v>
+        <v>9910</v>
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>德勝</t>
+          <t>豐泰</t>
         </is>
       </c>
       <c r="C87" s="2" t="n">
         <v/>
       </c>
       <c r="D87" s="2" t="n">
-        <v>220.9898481534327</v>
+        <v>225.9460424244129</v>
       </c>
       <c r="E87" s="2" t="n">
-        <v>59.1</v>
+        <v>67.8</v>
       </c>
       <c r="F87" s="2" t="inlineStr">
         <is>
@@ -5057,13 +5057,13 @@
         <v>0</v>
       </c>
       <c r="H87" s="2" t="n">
-        <v>39.83087722294104</v>
+        <v>41.89948994859546</v>
       </c>
       <c r="I87" s="2" t="n">
-        <v>12.8637754718167</v>
+        <v>18.81065289962456</v>
       </c>
       <c r="J87" s="2" t="n">
-        <v>0.817772946337338</v>
+        <v>0.3303295608426863</v>
       </c>
       <c r="K87" s="2" t="n">
         <v>0</v>
@@ -5075,31 +5075,31 @@
         <v>-1</v>
       </c>
       <c r="N87" s="2" t="n">
-        <v>-0.3518644796919655</v>
+        <v>-0.1382559520683939</v>
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="n">
-        <v>8076</v>
+        <v>8940</v>
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>伍豐</t>
+          <t>新天地</t>
         </is>
       </c>
       <c r="C88" s="2" t="n">
         <v/>
       </c>
       <c r="D88" s="2" t="n">
-        <v>207.4766294427554</v>
+        <v>224.0716528109438</v>
       </c>
       <c r="E88" s="2" t="n">
-        <v>24.05</v>
+        <v>16.25</v>
       </c>
       <c r="F88" s="2" t="inlineStr">
         <is>
@@ -5110,13 +5110,13 @@
         <v>0</v>
       </c>
       <c r="H88" s="2" t="n">
-        <v>40.51440601736444</v>
+        <v>41.47253265756475</v>
       </c>
       <c r="I88" s="2" t="n">
-        <v>14.12528841567118</v>
+        <v>19.11107886224</v>
       </c>
       <c r="J88" s="2" t="n">
-        <v>0.5887991655501763</v>
+        <v>0.5782847551515361</v>
       </c>
       <c r="K88" s="2" t="n">
         <v>0</v>
@@ -5128,31 +5128,31 @@
         <v>-1</v>
       </c>
       <c r="N88" s="2" t="n">
-        <v>-0.1868814702109589</v>
+        <v>-0.0122274209931299</v>
       </c>
       <c r="O88" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="n">
-        <v>8429</v>
+        <v>8048</v>
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>金麗-KY</t>
+          <t>德勝</t>
         </is>
       </c>
       <c r="C89" s="2" t="n">
         <v/>
       </c>
       <c r="D89" s="2" t="n">
-        <v>199.4930808749796</v>
+        <v>220.9898481534327</v>
       </c>
       <c r="E89" s="2" t="n">
-        <v>6.26</v>
+        <v>59.1</v>
       </c>
       <c r="F89" s="2" t="inlineStr">
         <is>
@@ -5163,13 +5163,13 @@
         <v>0</v>
       </c>
       <c r="H89" s="2" t="n">
-        <v>44.77101165691071</v>
+        <v>39.83087722294104</v>
       </c>
       <c r="I89" s="2" t="n">
-        <v>12.2484716411762</v>
+        <v>12.8637754718167</v>
       </c>
       <c r="J89" s="2" t="n">
-        <v>0.5193258892757937</v>
+        <v>0.817772946337338</v>
       </c>
       <c r="K89" s="2" t="n">
         <v>0</v>
@@ -5181,31 +5181,31 @@
         <v>-1</v>
       </c>
       <c r="N89" s="2" t="n">
-        <v>-0.0045384625231669</v>
+        <v>-0.3518644796919655</v>
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="n">
-        <v>8213</v>
+        <v>8076</v>
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>志超</t>
+          <t>伍豐</t>
         </is>
       </c>
       <c r="C90" s="2" t="n">
         <v/>
       </c>
       <c r="D90" s="2" t="n">
-        <v>199.4434125044632</v>
+        <v>207.4766294427553</v>
       </c>
       <c r="E90" s="2" t="n">
-        <v>34.1</v>
+        <v>24.05</v>
       </c>
       <c r="F90" s="2" t="inlineStr">
         <is>
@@ -5216,13 +5216,13 @@
         <v>0</v>
       </c>
       <c r="H90" s="2" t="n">
-        <v>39.67957050500144</v>
+        <v>40.51440601736444</v>
       </c>
       <c r="I90" s="2" t="n">
-        <v>19.86292552110228</v>
+        <v>14.12528841567118</v>
       </c>
       <c r="J90" s="2" t="n">
-        <v>0.4074518254838803</v>
+        <v>0.5887991655501763</v>
       </c>
       <c r="K90" s="2" t="n">
         <v>0</v>
@@ -5234,7 +5234,7 @@
         <v>-1</v>
       </c>
       <c r="N90" s="2" t="n">
-        <v>-0.1703094827224911</v>
+        <v>-0.1868814702109589</v>
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
@@ -5244,21 +5244,21 @@
     </row>
     <row r="91">
       <c r="A91" s="2" t="n">
-        <v>9955</v>
+        <v>8429</v>
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>佳龍</t>
+          <t>金麗-KY</t>
         </is>
       </c>
       <c r="C91" s="2" t="n">
         <v/>
       </c>
       <c r="D91" s="2" t="n">
-        <v>197.2174060599464</v>
+        <v>199.4930808749796</v>
       </c>
       <c r="E91" s="2" t="n">
-        <v>25.05</v>
+        <v>6.26</v>
       </c>
       <c r="F91" s="2" t="inlineStr">
         <is>
@@ -5269,13 +5269,13 @@
         <v>0</v>
       </c>
       <c r="H91" s="2" t="n">
-        <v>35.14359762942705</v>
+        <v>44.77101165691071</v>
       </c>
       <c r="I91" s="2" t="n">
-        <v>25.26763929918993</v>
+        <v>12.2484716411762</v>
       </c>
       <c r="J91" s="2" t="n">
-        <v>0.7909623122605393</v>
+        <v>0.5193258892757937</v>
       </c>
       <c r="K91" s="2" t="n">
         <v>0</v>
@@ -5287,31 +5287,31 @@
         <v>-1</v>
       </c>
       <c r="N91" s="2" t="n">
-        <v>-0.1120926227166068</v>
+        <v>-0.0045384625231669</v>
       </c>
       <c r="O91" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="n">
-        <v>9930</v>
+        <v>8213</v>
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>中聯資源</t>
+          <t>志超</t>
         </is>
       </c>
       <c r="C92" s="2" t="n">
         <v/>
       </c>
       <c r="D92" s="2" t="n">
-        <v>197.0479842419313</v>
+        <v>199.4434125044632</v>
       </c>
       <c r="E92" s="2" t="n">
-        <v>63.6</v>
+        <v>34.1</v>
       </c>
       <c r="F92" s="2" t="inlineStr">
         <is>
@@ -5322,13 +5322,13 @@
         <v>0</v>
       </c>
       <c r="H92" s="2" t="n">
-        <v>30.89009132422328</v>
+        <v>39.67957050500144</v>
       </c>
       <c r="I92" s="2" t="n">
-        <v>47.84302328762074</v>
+        <v>19.86292552110228</v>
       </c>
       <c r="J92" s="2" t="n">
-        <v>0.7515418088637074</v>
+        <v>0.4074518254838803</v>
       </c>
       <c r="K92" s="2" t="n">
         <v>0</v>
@@ -5340,31 +5340,31 @@
         <v>-1</v>
       </c>
       <c r="N92" s="2" t="n">
-        <v>-0.1620132817596766</v>
+        <v>-0.1703094827224911</v>
       </c>
       <c r="O92" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="n">
-        <v>8080</v>
+        <v>9955</v>
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>永利聯合</t>
+          <t>佳龍</t>
         </is>
       </c>
       <c r="C93" s="2" t="n">
         <v/>
       </c>
       <c r="D93" s="2" t="n">
-        <v>195.1639374347412</v>
+        <v>197.2174060599464</v>
       </c>
       <c r="E93" s="2" t="n">
-        <v>27.35</v>
+        <v>25.05</v>
       </c>
       <c r="F93" s="2" t="inlineStr">
         <is>
@@ -5375,13 +5375,13 @@
         <v>0</v>
       </c>
       <c r="H93" s="2" t="n">
-        <v>42.36470882434945</v>
+        <v>35.14359762942705</v>
       </c>
       <c r="I93" s="2" t="n">
-        <v>38.40175485177136</v>
+        <v>25.26763929918993</v>
       </c>
       <c r="J93" s="2" t="n">
-        <v>0.2968311914522448</v>
+        <v>0.7909623122605393</v>
       </c>
       <c r="K93" s="2" t="n">
         <v>0</v>
@@ -5393,7 +5393,7 @@
         <v>-1</v>
       </c>
       <c r="N93" s="2" t="n">
-        <v>-0.0594338526402684</v>
+        <v>-0.1120926227166068</v>
       </c>
       <c r="O93" s="2" t="inlineStr">
         <is>
@@ -5403,21 +5403,21 @@
     </row>
     <row r="94">
       <c r="A94" s="2" t="n">
-        <v>8341</v>
+        <v>9930</v>
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>日友</t>
+          <t>中聯資源</t>
         </is>
       </c>
       <c r="C94" s="2" t="n">
         <v/>
       </c>
       <c r="D94" s="2" t="n">
-        <v>195.0210894953262</v>
+        <v>197.0479842419313</v>
       </c>
       <c r="E94" s="2" t="n">
-        <v>77.09999999999999</v>
+        <v>63.6</v>
       </c>
       <c r="F94" s="2" t="inlineStr">
         <is>
@@ -5428,13 +5428,13 @@
         <v>0</v>
       </c>
       <c r="H94" s="2" t="n">
-        <v>49.84925242923595</v>
+        <v>30.89009132422328</v>
       </c>
       <c r="I94" s="2" t="n">
-        <v>16.47152710669021</v>
+        <v>47.84302328762074</v>
       </c>
       <c r="J94" s="2" t="n">
-        <v>1.096779214874101</v>
+        <v>0.7515418088637074</v>
       </c>
       <c r="K94" s="2" t="n">
         <v>0</v>
@@ -5446,31 +5446,31 @@
         <v>-1</v>
       </c>
       <c r="N94" s="2" t="n">
-        <v>-0.1037540014555359</v>
+        <v>-0.1620132817596766</v>
       </c>
       <c r="O94" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="n">
-        <v>8477</v>
+        <v>8080</v>
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>創業家</t>
+          <t>永利聯合</t>
         </is>
       </c>
       <c r="C95" s="2" t="n">
         <v/>
       </c>
       <c r="D95" s="2" t="n">
-        <v>190.6616329386668</v>
+        <v>195.1639374347412</v>
       </c>
       <c r="E95" s="2" t="n">
-        <v>15.8</v>
+        <v>27.35</v>
       </c>
       <c r="F95" s="2" t="inlineStr">
         <is>
@@ -5481,13 +5481,13 @@
         <v>0</v>
       </c>
       <c r="H95" s="2" t="n">
-        <v>41.16272696045727</v>
+        <v>42.36470882434945</v>
       </c>
       <c r="I95" s="2" t="n">
-        <v>13.1283731916111</v>
+        <v>38.40175485177136</v>
       </c>
       <c r="J95" s="2" t="n">
-        <v>0.3330992496419625</v>
+        <v>0.2968311914522448</v>
       </c>
       <c r="K95" s="2" t="n">
         <v>0</v>
@@ -5499,31 +5499,31 @@
         <v>-1</v>
       </c>
       <c r="N95" s="2" t="n">
-        <v>-0.0519061881192596</v>
+        <v>-0.0594338526402684</v>
       </c>
       <c r="O95" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="n">
-        <v>8422</v>
+        <v>8341</v>
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>可寧衛*</t>
+          <t>日友</t>
         </is>
       </c>
       <c r="C96" s="2" t="n">
         <v/>
       </c>
       <c r="D96" s="2" t="n">
-        <v>190.5524495921431</v>
+        <v>195.0210894953262</v>
       </c>
       <c r="E96" s="2" t="n">
-        <v>27</v>
+        <v>77.09999999999999</v>
       </c>
       <c r="F96" s="2" t="inlineStr">
         <is>
@@ -5534,13 +5534,13 @@
         <v>0</v>
       </c>
       <c r="H96" s="2" t="n">
-        <v>45.7341410192893</v>
+        <v>49.84925242923595</v>
       </c>
       <c r="I96" s="2" t="n">
-        <v>12.81394867914373</v>
+        <v>16.47152710669021</v>
       </c>
       <c r="J96" s="2" t="n">
-        <v>0.3214809236722823</v>
+        <v>1.096779214874101</v>
       </c>
       <c r="K96" s="2" t="n">
         <v>0</v>
@@ -5552,31 +5552,31 @@
         <v>-1</v>
       </c>
       <c r="N96" s="2" t="n">
-        <v>-0.1563759949776289</v>
+        <v>-0.1037540014555359</v>
       </c>
       <c r="O96" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>market_above_ma60, avoid_chase, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="n">
-        <v>8472</v>
+        <v>8477</v>
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>夠麻吉</t>
+          <t>創業家</t>
         </is>
       </c>
       <c r="C97" s="2" t="n">
         <v/>
       </c>
       <c r="D97" s="2" t="n">
-        <v>171.5877237892778</v>
+        <v>190.6616329386668</v>
       </c>
       <c r="E97" s="2" t="n">
-        <v>79</v>
+        <v>15.8</v>
       </c>
       <c r="F97" s="2" t="inlineStr">
         <is>
@@ -5587,13 +5587,13 @@
         <v>0</v>
       </c>
       <c r="H97" s="2" t="n">
-        <v>44.56465534303395</v>
+        <v>41.16272696045727</v>
       </c>
       <c r="I97" s="2" t="n">
-        <v>13.30810063265904</v>
+        <v>13.1283731916111</v>
       </c>
       <c r="J97" s="2" t="n">
-        <v>2.397512110519706</v>
+        <v>0.3330992496419625</v>
       </c>
       <c r="K97" s="2" t="n">
         <v>0</v>
@@ -5605,31 +5605,31 @@
         <v>-1</v>
       </c>
       <c r="N97" s="2" t="n">
-        <v>-0.5442482093128996</v>
+        <v>-0.0519061881192596</v>
       </c>
       <c r="O97" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="n">
-        <v>8085</v>
+        <v>8422</v>
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>福華</t>
+          <t>可寧衛*</t>
         </is>
       </c>
       <c r="C98" s="2" t="n">
         <v/>
       </c>
       <c r="D98" s="2" t="n">
-        <v>170.8756576622547</v>
+        <v>190.5524495921431</v>
       </c>
       <c r="E98" s="2" t="n">
-        <v>11.3</v>
+        <v>27</v>
       </c>
       <c r="F98" s="2" t="inlineStr">
         <is>
@@ -5640,13 +5640,13 @@
         <v>0</v>
       </c>
       <c r="H98" s="2" t="n">
-        <v>38.81258561168202</v>
+        <v>45.7341410192893</v>
       </c>
       <c r="I98" s="2" t="n">
-        <v>19.74921598635633</v>
+        <v>12.81394867914373</v>
       </c>
       <c r="J98" s="2" t="n">
-        <v>0.3104777000825021</v>
+        <v>0.3214809236722823</v>
       </c>
       <c r="K98" s="2" t="n">
         <v>0</v>
@@ -5658,31 +5658,31 @@
         <v>-1</v>
       </c>
       <c r="N98" s="2" t="n">
-        <v>-0.0682603885937825</v>
+        <v>-0.1563759949776289</v>
       </c>
       <c r="O98" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="2" t="n">
-        <v>8097</v>
+        <v>8472</v>
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>常珵</t>
+          <t>夠麻吉</t>
         </is>
       </c>
       <c r="C99" s="2" t="n">
         <v/>
       </c>
       <c r="D99" s="2" t="n">
-        <v>170.6027731534674</v>
+        <v>171.5877237892778</v>
       </c>
       <c r="E99" s="2" t="n">
-        <v>54.4</v>
+        <v>79</v>
       </c>
       <c r="F99" s="2" t="inlineStr">
         <is>
@@ -5693,13 +5693,13 @@
         <v>0</v>
       </c>
       <c r="H99" s="2" t="n">
-        <v>34.39203346491674</v>
+        <v>44.56465534303395</v>
       </c>
       <c r="I99" s="2" t="n">
-        <v>13.44930608382976</v>
+        <v>13.30810063265904</v>
       </c>
       <c r="J99" s="2" t="n">
-        <v>0.0759569877146605</v>
+        <v>2.397512110519706</v>
       </c>
       <c r="K99" s="2" t="n">
         <v>0</v>
@@ -5711,31 +5711,31 @@
         <v>-1</v>
       </c>
       <c r="N99" s="2" t="n">
-        <v>-0.5416797352244528</v>
+        <v>-0.5442482093128996</v>
       </c>
       <c r="O99" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase</t>
+          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="n">
-        <v>8087</v>
+        <v>8085</v>
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>華鎂鑫</t>
+          <t>福華</t>
         </is>
       </c>
       <c r="C100" s="2" t="n">
         <v/>
       </c>
       <c r="D100" s="2" t="n">
-        <v>167.607122113725</v>
+        <v>170.8756576622547</v>
       </c>
       <c r="E100" s="2" t="n">
-        <v>29.15</v>
+        <v>11.3</v>
       </c>
       <c r="F100" s="2" t="inlineStr">
         <is>
@@ -5746,13 +5746,13 @@
         <v>0</v>
       </c>
       <c r="H100" s="2" t="n">
-        <v>28.60444467986188</v>
+        <v>38.81258561168202</v>
       </c>
       <c r="I100" s="2" t="n">
-        <v>12.25444844865429</v>
+        <v>19.74921598635633</v>
       </c>
       <c r="J100" s="2" t="n">
-        <v>0.2972042238579426</v>
+        <v>0.3104777000825021</v>
       </c>
       <c r="K100" s="2" t="n">
         <v>0</v>
@@ -5764,31 +5764,31 @@
         <v>-1</v>
       </c>
       <c r="N100" s="2" t="n">
-        <v>-0.301530629366708</v>
+        <v>-0.0682603885937825</v>
       </c>
       <c r="O100" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="2" t="n">
-        <v>8423</v>
+        <v>8097</v>
       </c>
       <c r="B101" s="2" t="inlineStr">
         <is>
-          <t>保綠-KY</t>
+          <t>常珵</t>
         </is>
       </c>
       <c r="C101" s="2" t="n">
         <v/>
       </c>
       <c r="D101" s="2" t="n">
-        <v>161.7943974383586</v>
+        <v>170.6027731534674</v>
       </c>
       <c r="E101" s="2" t="n">
-        <v>17.7</v>
+        <v>54.4</v>
       </c>
       <c r="F101" s="2" t="inlineStr">
         <is>
@@ -5799,13 +5799,13 @@
         <v>0</v>
       </c>
       <c r="H101" s="2" t="n">
-        <v>49.15519204542669</v>
+        <v>34.39203346491674</v>
       </c>
       <c r="I101" s="2" t="n">
-        <v>11.25666602996415</v>
+        <v>13.44930608382976</v>
       </c>
       <c r="J101" s="2" t="n">
-        <v>0.212739203897992</v>
+        <v>0.0759569877146605</v>
       </c>
       <c r="K101" s="2" t="n">
         <v>0</v>
@@ -5817,7 +5817,7 @@
         <v>-1</v>
       </c>
       <c r="N101" s="2" t="n">
-        <v>-0.0028578483299899</v>
+        <v>-0.5416797352244528</v>
       </c>
       <c r="O101" s="2" t="inlineStr">
         <is>
@@ -5827,21 +5827,21 @@
     </row>
     <row r="102">
       <c r="A102" s="2" t="n">
-        <v>8277</v>
+        <v>8087</v>
       </c>
       <c r="B102" s="2" t="inlineStr">
         <is>
-          <t>商丞</t>
+          <t>華鎂鑫</t>
         </is>
       </c>
       <c r="C102" s="2" t="n">
         <v/>
       </c>
       <c r="D102" s="2" t="n">
-        <v>155.4676255592909</v>
+        <v>167.607122113725</v>
       </c>
       <c r="E102" s="2" t="n">
-        <v>8.41</v>
+        <v>29.15</v>
       </c>
       <c r="F102" s="2" t="inlineStr">
         <is>
@@ -5852,13 +5852,13 @@
         <v>0</v>
       </c>
       <c r="H102" s="2" t="n">
-        <v>39.96809458875105</v>
+        <v>28.60444467986188</v>
       </c>
       <c r="I102" s="2" t="n">
-        <v>24.56825611087597</v>
+        <v>12.25444844865429</v>
       </c>
       <c r="J102" s="2" t="n">
-        <v>0.1822681980422034</v>
+        <v>0.2972042238579426</v>
       </c>
       <c r="K102" s="2" t="n">
         <v>0</v>
@@ -5870,31 +5870,31 @@
         <v>-1</v>
       </c>
       <c r="N102" s="2" t="n">
-        <v>-0.1998305885217701</v>
+        <v>-0.301530629366708</v>
       </c>
       <c r="O102" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="2" t="n">
-        <v>9802</v>
+        <v>8423</v>
       </c>
       <c r="B103" s="2" t="inlineStr">
         <is>
-          <t>鈺齊-KY</t>
+          <t>保綠-KY</t>
         </is>
       </c>
       <c r="C103" s="2" t="n">
         <v/>
       </c>
       <c r="D103" s="2" t="n">
-        <v>151.9988473109074</v>
+        <v>161.7943974383586</v>
       </c>
       <c r="E103" s="2" t="n">
-        <v>75.90000000000001</v>
+        <v>17.7</v>
       </c>
       <c r="F103" s="2" t="inlineStr">
         <is>
@@ -5905,13 +5905,13 @@
         <v>0</v>
       </c>
       <c r="H103" s="2" t="n">
-        <v>52.70637624471667</v>
+        <v>49.15519204542669</v>
       </c>
       <c r="I103" s="2" t="n">
-        <v>11.67135651765832</v>
+        <v>11.25666602996415</v>
       </c>
       <c r="J103" s="2" t="n">
-        <v>0.9760602485930758</v>
+        <v>0.212739203897992</v>
       </c>
       <c r="K103" s="2" t="n">
         <v>0</v>
@@ -5923,7 +5923,7 @@
         <v>-1</v>
       </c>
       <c r="N103" s="2" t="n">
-        <v>0.2906598304488573</v>
+        <v>-0.0028578483299899</v>
       </c>
       <c r="O103" s="2" t="inlineStr">
         <is>
@@ -5933,21 +5933,21 @@
     </row>
     <row r="104">
       <c r="A104" s="2" t="n">
-        <v>8072</v>
+        <v>8277</v>
       </c>
       <c r="B104" s="2" t="inlineStr">
         <is>
-          <t>陞泰</t>
+          <t>商丞</t>
         </is>
       </c>
       <c r="C104" s="2" t="n">
         <v/>
       </c>
       <c r="D104" s="2" t="n">
-        <v>150.9460908936894</v>
+        <v>155.4676255592909</v>
       </c>
       <c r="E104" s="2" t="n">
-        <v>28.2</v>
+        <v>8.41</v>
       </c>
       <c r="F104" s="2" t="inlineStr">
         <is>
@@ -5958,13 +5958,13 @@
         <v>0</v>
       </c>
       <c r="H104" s="2" t="n">
-        <v>44.83356728107118</v>
+        <v>39.96809458875105</v>
       </c>
       <c r="I104" s="2" t="n">
-        <v>18.62554393880958</v>
+        <v>24.56825611087597</v>
       </c>
       <c r="J104" s="2" t="n">
-        <v>1.181181268254654</v>
+        <v>0.1822681980422034</v>
       </c>
       <c r="K104" s="2" t="n">
         <v>0</v>
@@ -5976,31 +5976,31 @@
         <v>-1</v>
       </c>
       <c r="N104" s="2" t="n">
-        <v>-0.1885101816107047</v>
+        <v>-0.1998305885217701</v>
       </c>
       <c r="O104" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="2" t="n">
-        <v>9103</v>
+        <v>9802</v>
       </c>
       <c r="B105" s="2" t="inlineStr">
         <is>
-          <t>美德醫療-DR</t>
+          <t>鈺齊-KY</t>
         </is>
       </c>
       <c r="C105" s="2" t="n">
         <v/>
       </c>
       <c r="D105" s="2" t="n">
-        <v>150.870855847214</v>
+        <v>151.9988473109074</v>
       </c>
       <c r="E105" s="2" t="n">
-        <v>5.07</v>
+        <v>75.90000000000001</v>
       </c>
       <c r="F105" s="2" t="inlineStr">
         <is>
@@ -6011,13 +6011,13 @@
         <v>0</v>
       </c>
       <c r="H105" s="2" t="n">
-        <v>45.82464513880021</v>
+        <v>52.70637624471667</v>
       </c>
       <c r="I105" s="2" t="n">
-        <v>13.54031969814969</v>
+        <v>11.67135651765832</v>
       </c>
       <c r="J105" s="2" t="n">
-        <v>0.6002977151651521</v>
+        <v>0.9760602485930758</v>
       </c>
       <c r="K105" s="2" t="n">
         <v>0</v>
@@ -6029,31 +6029,31 @@
         <v>-1</v>
       </c>
       <c r="N105" s="2" t="n">
-        <v>-0.0170999891987256</v>
+        <v>0.2906598304488573</v>
       </c>
       <c r="O105" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="2" t="n">
-        <v>8249</v>
+        <v>8072</v>
       </c>
       <c r="B106" s="2" t="inlineStr">
         <is>
-          <t>菱光</t>
+          <t>陞泰</t>
         </is>
       </c>
       <c r="C106" s="2" t="n">
         <v/>
       </c>
       <c r="D106" s="2" t="n">
-        <v>141.9365014731906</v>
+        <v>150.9460908936894</v>
       </c>
       <c r="E106" s="2" t="n">
-        <v>46.65</v>
+        <v>28.2</v>
       </c>
       <c r="F106" s="2" t="inlineStr">
         <is>
@@ -6064,13 +6064,13 @@
         <v>0</v>
       </c>
       <c r="H106" s="2" t="n">
-        <v>37.91320064976643</v>
+        <v>44.83356728107118</v>
       </c>
       <c r="I106" s="2" t="n">
-        <v>13.52813869761969</v>
+        <v>18.62554393880958</v>
       </c>
       <c r="J106" s="2" t="n">
-        <v>0.2719333135877078</v>
+        <v>1.181181268254654</v>
       </c>
       <c r="K106" s="2" t="n">
         <v>0</v>
@@ -6082,7 +6082,7 @@
         <v>-1</v>
       </c>
       <c r="N106" s="2" t="n">
-        <v>-0.0871446852809438</v>
+        <v>-0.1885101816107047</v>
       </c>
       <c r="O106" s="2" t="inlineStr">
         <is>
@@ -6092,21 +6092,21 @@
     </row>
     <row r="107">
       <c r="A107" s="2" t="n">
-        <v>8487</v>
+        <v>9103</v>
       </c>
       <c r="B107" s="2" t="inlineStr">
         <is>
-          <t>愛爾達-創</t>
+          <t>美德醫療-DR</t>
         </is>
       </c>
       <c r="C107" s="2" t="n">
         <v/>
       </c>
       <c r="D107" s="2" t="n">
-        <v>141.5864745516106</v>
+        <v>150.870855847214</v>
       </c>
       <c r="E107" s="2" t="n">
-        <v>76.90000000000001</v>
+        <v>5.07</v>
       </c>
       <c r="F107" s="2" t="inlineStr">
         <is>
@@ -6117,13 +6117,13 @@
         <v>0</v>
       </c>
       <c r="H107" s="2" t="n">
-        <v>43.15889260624053</v>
+        <v>45.82464513880021</v>
       </c>
       <c r="I107" s="2" t="n">
-        <v>12.52424180980612</v>
+        <v>13.54031969814969</v>
       </c>
       <c r="J107" s="2" t="n">
-        <v>0.5001590471912812</v>
+        <v>0.6002977151651521</v>
       </c>
       <c r="K107" s="2" t="n">
         <v>0</v>
@@ -6135,31 +6135,31 @@
         <v>-1</v>
       </c>
       <c r="N107" s="2" t="n">
-        <v>-0.1739093327655101</v>
+        <v>-0.0170999891987256</v>
       </c>
       <c r="O107" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="2" t="n">
-        <v>9902</v>
+        <v>8249</v>
       </c>
       <c r="B108" s="2" t="inlineStr">
         <is>
-          <t>台火</t>
+          <t>菱光</t>
         </is>
       </c>
       <c r="C108" s="2" t="n">
         <v/>
       </c>
       <c r="D108" s="2" t="n">
-        <v>127.0186671649767</v>
+        <v>141.9365014731906</v>
       </c>
       <c r="E108" s="2" t="n">
-        <v>13.9</v>
+        <v>46.65</v>
       </c>
       <c r="F108" s="2" t="inlineStr">
         <is>
@@ -6170,13 +6170,13 @@
         <v>0</v>
       </c>
       <c r="H108" s="2" t="n">
-        <v>51.74839635834162</v>
+        <v>37.91320064976643</v>
       </c>
       <c r="I108" s="2" t="n">
-        <v>15.27462290359012</v>
+        <v>13.52813869761969</v>
       </c>
       <c r="J108" s="2" t="n">
-        <v>0.5445138622593415</v>
+        <v>0.2719333135877078</v>
       </c>
       <c r="K108" s="2" t="n">
         <v>0</v>
@@ -6188,7 +6188,7 @@
         <v>-1</v>
       </c>
       <c r="N108" s="2" t="n">
-        <v>0.0267816586214377</v>
+        <v>-0.0871446852809438</v>
       </c>
       <c r="O108" s="2" t="inlineStr">
         <is>
@@ -6198,21 +6198,21 @@
     </row>
     <row r="109">
       <c r="A109" s="2" t="n">
-        <v>8054</v>
+        <v>8487</v>
       </c>
       <c r="B109" s="2" t="inlineStr">
         <is>
-          <t>安國</t>
+          <t>愛爾達-創</t>
         </is>
       </c>
       <c r="C109" s="2" t="n">
         <v/>
       </c>
       <c r="D109" s="2" t="n">
-        <v>118.3380218211552</v>
+        <v>141.5864745516106</v>
       </c>
       <c r="E109" s="2" t="n">
-        <v>95.90000000000001</v>
+        <v>76.90000000000001</v>
       </c>
       <c r="F109" s="2" t="inlineStr">
         <is>
@@ -6223,13 +6223,13 @@
         <v>0</v>
       </c>
       <c r="H109" s="2" t="n">
-        <v>38.65166593860749</v>
+        <v>43.15889260624053</v>
       </c>
       <c r="I109" s="2" t="n">
-        <v>19.86417629633029</v>
+        <v>12.52424180980612</v>
       </c>
       <c r="J109" s="2" t="n">
-        <v>0.2557691389078973</v>
+        <v>0.5001590471912812</v>
       </c>
       <c r="K109" s="2" t="n">
         <v>0</v>
@@ -6241,31 +6241,31 @@
         <v>-1</v>
       </c>
       <c r="N109" s="2" t="n">
-        <v>-2.540917017443375</v>
+        <v>-0.1739093327655101</v>
       </c>
       <c r="O109" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="2" t="n">
-        <v>8092</v>
+        <v>9902</v>
       </c>
       <c r="B110" s="2" t="inlineStr">
         <is>
-          <t>建暐</t>
+          <t>台火</t>
         </is>
       </c>
       <c r="C110" s="2" t="n">
         <v/>
       </c>
       <c r="D110" s="2" t="n">
-        <v>116.1145667635546</v>
+        <v>127.0186671649767</v>
       </c>
       <c r="E110" s="2" t="n">
-        <v>13.95</v>
+        <v>13.9</v>
       </c>
       <c r="F110" s="2" t="inlineStr">
         <is>
@@ -6276,16 +6276,16 @@
         <v>0</v>
       </c>
       <c r="H110" s="2" t="n">
-        <v>42.82473805916636</v>
+        <v>51.74839635834162</v>
       </c>
       <c r="I110" s="2" t="n">
-        <v>14.9595234055055</v>
+        <v>15.27462290359012</v>
       </c>
       <c r="J110" s="2" t="n">
-        <v>0.9227393614279026</v>
+        <v>0.5445138622593415</v>
       </c>
       <c r="K110" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L110" s="2" t="n">
         <v>0</v>
@@ -6294,7 +6294,7 @@
         <v>-1</v>
       </c>
       <c r="N110" s="2" t="n">
-        <v>0.0746012629753374</v>
+        <v>0.0267816586214377</v>
       </c>
       <c r="O110" s="2" t="inlineStr">
         <is>
@@ -6304,21 +6304,21 @@
     </row>
     <row r="111">
       <c r="A111" s="2" t="n">
-        <v>8467</v>
+        <v>8054</v>
       </c>
       <c r="B111" s="2" t="inlineStr">
         <is>
-          <t>波力-KY</t>
+          <t>安國</t>
         </is>
       </c>
       <c r="C111" s="2" t="n">
         <v/>
       </c>
       <c r="D111" s="2" t="n">
-        <v>91.27119946273446</v>
+        <v>118.3380218211552</v>
       </c>
       <c r="E111" s="2" t="n">
-        <v>106.5</v>
+        <v>95.90000000000001</v>
       </c>
       <c r="F111" s="2" t="inlineStr">
         <is>
@@ -6329,13 +6329,13 @@
         <v>0</v>
       </c>
       <c r="H111" s="2" t="n">
-        <v>43.72445199450566</v>
+        <v>38.65166593860749</v>
       </c>
       <c r="I111" s="2" t="n">
-        <v>11.44417625708494</v>
+        <v>19.86417629633029</v>
       </c>
       <c r="J111" s="2" t="n">
-        <v>1.237828393981445</v>
+        <v>0.2557691389078973</v>
       </c>
       <c r="K111" s="2" t="n">
         <v>0</v>
@@ -6347,31 +6347,31 @@
         <v>-1</v>
       </c>
       <c r="N111" s="2" t="n">
-        <v>-0.3263000597864884</v>
+        <v>-2.540917017443375</v>
       </c>
       <c r="O111" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="2" t="n">
-        <v>9110</v>
+        <v>8092</v>
       </c>
       <c r="B112" s="2" t="inlineStr">
         <is>
-          <t>越南控-DR</t>
+          <t>建暐</t>
         </is>
       </c>
       <c r="C112" s="2" t="n">
         <v/>
       </c>
       <c r="D112" s="2" t="n">
-        <v>85.81603592631038</v>
+        <v>116.1145667635546</v>
       </c>
       <c r="E112" s="2" t="n">
-        <v>3.14</v>
+        <v>13.95</v>
       </c>
       <c r="F112" s="2" t="inlineStr">
         <is>
@@ -6382,16 +6382,16 @@
         <v>0</v>
       </c>
       <c r="H112" s="2" t="n">
-        <v>50.60560480073277</v>
+        <v>42.82473805916636</v>
       </c>
       <c r="I112" s="2" t="n">
-        <v>8.532427974009856</v>
+        <v>14.9595234055055</v>
       </c>
       <c r="J112" s="2" t="n">
-        <v>0.0375585443810539</v>
+        <v>0.9227393614279026</v>
       </c>
       <c r="K112" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L112" s="2" t="n">
         <v>0</v>
@@ -6400,7 +6400,7 @@
         <v>-1</v>
       </c>
       <c r="N112" s="2" t="n">
-        <v>0.0191586820072735</v>
+        <v>0.0746012629753374</v>
       </c>
       <c r="O112" s="2" t="inlineStr">
         <is>
@@ -6410,21 +6410,21 @@
     </row>
     <row r="113">
       <c r="A113" s="2" t="n">
-        <v>8410</v>
+        <v>8467</v>
       </c>
       <c r="B113" s="2" t="inlineStr">
         <is>
-          <t>森田</t>
+          <t>波力-KY</t>
         </is>
       </c>
       <c r="C113" s="2" t="n">
         <v/>
       </c>
       <c r="D113" s="2" t="n">
-        <v>76.48168449287203</v>
+        <v>91.27119946273446</v>
       </c>
       <c r="E113" s="2" t="n">
-        <v>32.75</v>
+        <v>106.5</v>
       </c>
       <c r="F113" s="2" t="inlineStr">
         <is>
@@ -6435,13 +6435,13 @@
         <v>0</v>
       </c>
       <c r="H113" s="2" t="n">
-        <v>42.49558709993448</v>
+        <v>43.72445199450566</v>
       </c>
       <c r="I113" s="2" t="n">
-        <v>14.88140491244675</v>
+        <v>11.44417625708494</v>
       </c>
       <c r="J113" s="2" t="n">
-        <v>0.4222580012026534</v>
+        <v>1.237828393981445</v>
       </c>
       <c r="K113" s="2" t="n">
         <v>0</v>
@@ -6453,7 +6453,7 @@
         <v>-1</v>
       </c>
       <c r="N113" s="2" t="n">
-        <v>0.0706672408549002</v>
+        <v>-0.3263000597864884</v>
       </c>
       <c r="O113" s="2" t="inlineStr">
         <is>
@@ -6463,21 +6463,21 @@
     </row>
     <row r="114">
       <c r="A114" s="2" t="n">
-        <v>8431</v>
+        <v>9110</v>
       </c>
       <c r="B114" s="2" t="inlineStr">
         <is>
-          <t>匯鑽科</t>
+          <t>越南控-DR</t>
         </is>
       </c>
       <c r="C114" s="2" t="n">
         <v/>
       </c>
       <c r="D114" s="2" t="n">
-        <v>69.98377256209591</v>
+        <v>85.81603592631038</v>
       </c>
       <c r="E114" s="2" t="n">
-        <v>48.05</v>
+        <v>3.14</v>
       </c>
       <c r="F114" s="2" t="inlineStr">
         <is>
@@ -6488,13 +6488,13 @@
         <v>0</v>
       </c>
       <c r="H114" s="2" t="n">
-        <v>36.9139617978332</v>
+        <v>50.60560480073277</v>
       </c>
       <c r="I114" s="2" t="n">
-        <v>14.71937503655208</v>
+        <v>8.532427974009856</v>
       </c>
       <c r="J114" s="2" t="n">
-        <v>0.3445293679929196</v>
+        <v>0.0375585443810539</v>
       </c>
       <c r="K114" s="2" t="n">
         <v>0</v>
@@ -6506,7 +6506,7 @@
         <v>-1</v>
       </c>
       <c r="N114" s="2" t="n">
-        <v>-0.3395217731907261</v>
+        <v>0.0191586820072735</v>
       </c>
       <c r="O114" s="2" t="inlineStr">
         <is>
@@ -6516,52 +6516,158 @@
     </row>
     <row r="115">
       <c r="A115" s="2" t="n">
+        <v>8410</v>
+      </c>
+      <c r="B115" s="2" t="inlineStr">
+        <is>
+          <t>森田</t>
+        </is>
+      </c>
+      <c r="C115" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D115" s="2" t="n">
+        <v>76.48168449287203</v>
+      </c>
+      <c r="E115" s="2" t="n">
+        <v>32.75</v>
+      </c>
+      <c r="F115" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="G115" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H115" s="2" t="n">
+        <v>42.49558709993448</v>
+      </c>
+      <c r="I115" s="2" t="n">
+        <v>14.88140491244675</v>
+      </c>
+      <c r="J115" s="2" t="n">
+        <v>0.4222580012026534</v>
+      </c>
+      <c r="K115" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L115" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M115" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N115" s="2" t="n">
+        <v>0.0706672408549002</v>
+      </c>
+      <c r="O115" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="2" t="n">
+        <v>8431</v>
+      </c>
+      <c r="B116" s="2" t="inlineStr">
+        <is>
+          <t>匯鑽科</t>
+        </is>
+      </c>
+      <c r="C116" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D116" s="2" t="n">
+        <v>69.98377256209591</v>
+      </c>
+      <c r="E116" s="2" t="n">
+        <v>48.05</v>
+      </c>
+      <c r="F116" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="G116" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H116" s="2" t="n">
+        <v>36.9139617978332</v>
+      </c>
+      <c r="I116" s="2" t="n">
+        <v>14.71937503655208</v>
+      </c>
+      <c r="J116" s="2" t="n">
+        <v>0.3445293679929196</v>
+      </c>
+      <c r="K116" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L116" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M116" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N116" s="2" t="n">
+        <v>-0.3395217731907261</v>
+      </c>
+      <c r="O116" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="n">
         <v>8463</v>
       </c>
-      <c r="B115" s="2" t="inlineStr">
+      <c r="B117" s="2" t="inlineStr">
         <is>
           <t>潤泰材</t>
         </is>
       </c>
-      <c r="C115" s="2" t="n">
-        <v/>
-      </c>
-      <c r="D115" s="2" t="n">
+      <c r="C117" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D117" s="2" t="n">
         <v>64.39556268486805</v>
       </c>
-      <c r="E115" s="2" t="n">
+      <c r="E117" s="2" t="n">
         <v>21.6</v>
       </c>
-      <c r="F115" s="2" t="inlineStr">
-        <is>
-          <t>2026-07-16</t>
-        </is>
-      </c>
-      <c r="G115" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="H115" s="2" t="n">
+      <c r="F117" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="G117" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H117" s="2" t="n">
         <v>50.16003584956738</v>
       </c>
-      <c r="I115" s="2" t="n">
+      <c r="I117" s="2" t="n">
         <v>11.36843818231938</v>
       </c>
-      <c r="J115" s="2" t="n">
+      <c r="J117" s="2" t="n">
         <v>0.435444379970382</v>
       </c>
-      <c r="K115" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L115" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M115" s="2" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N115" s="2" t="n">
+      <c r="K117" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L117" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M117" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N117" s="2" t="n">
         <v>0.0276189344619608</v>
       </c>
-      <c r="O115" s="2" t="inlineStr">
+      <c r="O117" s="2" t="inlineStr">
         <is>
           <t>market_above_ma60, avoid_chase</t>
         </is>
